--- a/DECISION/미장_반도체_분석.xlsx
+++ b/DECISION/미장_반도체_분석.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="29">
   <si>
     <t>날짜</t>
   </si>
@@ -61,43 +61,40 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2025-12-06</t>
+    <t>2025-12-10</t>
+  </si>
+  <si>
+    <t>NVIDIA Corporation</t>
+  </si>
+  <si>
+    <t>Taiwan Semiconductor Manufactur</t>
   </si>
   <si>
     <t>ASML Holding N.V. - New York Re</t>
   </si>
   <si>
-    <t>Taiwan Semiconductor Manufactur</t>
-  </si>
-  <si>
     <t>Advanced Micro Devices, Inc.</t>
   </si>
   <si>
-    <t>NVIDIA Corporation</t>
-  </si>
-  <si>
     <t>QUALCOMM Incorporated</t>
   </si>
   <si>
+    <t>NVDA</t>
+  </si>
+  <si>
+    <t>TSM</t>
+  </si>
+  <si>
     <t>ASML</t>
   </si>
   <si>
-    <t>TSM</t>
-  </si>
-  <si>
     <t>AMD</t>
   </si>
   <si>
-    <t>NVDA</t>
-  </si>
-  <si>
     <t>QCOM</t>
   </si>
   <si>
     <t>Pattern</t>
-  </si>
-  <si>
-    <t>📈 매수 관찰 구간입니다.</t>
   </si>
   <si>
     <t>⛔ 관망하십시오.</t>
@@ -522,28 +519,28 @@
         <v>21</v>
       </c>
       <c r="D2">
-        <v>1099.47</v>
+        <v>184.88</v>
       </c>
       <c r="E2">
-        <v>63.1</v>
+        <v>54.2</v>
       </c>
       <c r="F2">
-        <v>3.72</v>
+        <v>1.89</v>
       </c>
       <c r="G2">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H2">
         <v>63</v>
       </c>
       <c r="I2">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="J2">
         <v>66</v>
       </c>
       <c r="K2">
-        <v>64.09999999999999</v>
+        <v>55.8</v>
       </c>
       <c r="L2" t="s">
         <v>26</v>
@@ -552,10 +549,10 @@
         <v>27</v>
       </c>
       <c r="N2">
-        <v>52.28493729186943</v>
+        <v>48.11568981226033</v>
       </c>
       <c r="O2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -569,40 +566,40 @@
         <v>22</v>
       </c>
       <c r="D3">
-        <v>294.72</v>
+        <v>303.93</v>
       </c>
       <c r="E3">
-        <v>59.7</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="F3">
-        <v>1.1</v>
+        <v>4.05</v>
       </c>
       <c r="G3">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="H3">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="I3">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="J3">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="K3">
-        <v>58.9</v>
+        <v>55.6</v>
       </c>
       <c r="L3" t="s">
         <v>26</v>
       </c>
       <c r="M3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N3">
+        <v>48.11568981226033</v>
+      </c>
+      <c r="O3" t="s">
         <v>28</v>
-      </c>
-      <c r="N3">
-        <v>52.28493729186943</v>
-      </c>
-      <c r="O3" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -616,40 +613,40 @@
         <v>23</v>
       </c>
       <c r="D4">
-        <v>217.97</v>
+        <v>1110.97</v>
       </c>
       <c r="E4">
-        <v>33.5</v>
+        <v>65.2</v>
       </c>
       <c r="F4">
         <v>0.2</v>
       </c>
       <c r="G4">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="H4">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="I4">
-        <v>86</v>
+        <v>56</v>
       </c>
       <c r="J4">
-        <v>76</v>
+        <v>56</v>
       </c>
       <c r="K4">
-        <v>56.1</v>
+        <v>54.8</v>
       </c>
       <c r="L4" t="s">
         <v>26</v>
       </c>
       <c r="M4" t="s">
+        <v>27</v>
+      </c>
+      <c r="N4">
+        <v>48.11568981226033</v>
+      </c>
+      <c r="O4" t="s">
         <v>28</v>
-      </c>
-      <c r="N4">
-        <v>52.28493729186943</v>
-      </c>
-      <c r="O4" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -663,40 +660,40 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>182.41</v>
+        <v>222.65</v>
       </c>
       <c r="E5">
-        <v>41.7</v>
+        <v>44.9</v>
       </c>
       <c r="F5">
-        <v>3.06</v>
+        <v>3.44</v>
       </c>
       <c r="G5">
         <v>30</v>
       </c>
       <c r="H5">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="I5">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="J5">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="K5">
-        <v>51.1</v>
+        <v>51.4</v>
       </c>
       <c r="L5" t="s">
         <v>26</v>
       </c>
       <c r="M5" t="s">
+        <v>27</v>
+      </c>
+      <c r="N5">
+        <v>48.11568981226033</v>
+      </c>
+      <c r="O5" t="s">
         <v>28</v>
-      </c>
-      <c r="N5">
-        <v>52.28493729186943</v>
-      </c>
-      <c r="O5" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:15">
@@ -710,19 +707,19 @@
         <v>25</v>
       </c>
       <c r="D6">
-        <v>174.81</v>
+        <v>175.54</v>
       </c>
       <c r="E6">
-        <v>52.4</v>
+        <v>70.3</v>
       </c>
       <c r="F6">
-        <v>4.53</v>
+        <v>3.36</v>
       </c>
       <c r="G6">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H6">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="I6">
         <v>36</v>
@@ -731,19 +728,19 @@
         <v>43</v>
       </c>
       <c r="K6">
-        <v>48.1</v>
+        <v>43.8</v>
       </c>
       <c r="L6" t="s">
         <v>26</v>
       </c>
       <c r="M6" t="s">
+        <v>27</v>
+      </c>
+      <c r="N6">
+        <v>48.11568981226033</v>
+      </c>
+      <c r="O6" t="s">
         <v>28</v>
-      </c>
-      <c r="N6">
-        <v>52.28493729186943</v>
-      </c>
-      <c r="O6" t="s">
-        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/DECISION/미장_반도체_분석.xlsx
+++ b/DECISION/미장_반도체_분석.xlsx
@@ -64,12 +64,12 @@
     <t>2025-12-10</t>
   </si>
   <si>
+    <t>Taiwan Semiconductor Manufactur</t>
+  </si>
+  <si>
     <t>NVIDIA Corporation</t>
   </si>
   <si>
-    <t>Taiwan Semiconductor Manufactur</t>
-  </si>
-  <si>
     <t>ASML Holding N.V. - New York Re</t>
   </si>
   <si>
@@ -79,10 +79,10 @@
     <t>QUALCOMM Incorporated</t>
   </si>
   <si>
+    <t>TSM</t>
+  </si>
+  <si>
     <t>NVDA</t>
-  </si>
-  <si>
-    <t>TSM</t>
   </si>
   <si>
     <t>ASML</t>
@@ -519,28 +519,28 @@
         <v>21</v>
       </c>
       <c r="D2">
-        <v>184.88</v>
+        <v>303.41</v>
       </c>
       <c r="E2">
-        <v>54.2</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="F2">
-        <v>1.89</v>
+        <v>3.88</v>
       </c>
       <c r="G2">
         <v>50</v>
       </c>
       <c r="H2">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="I2">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="J2">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="K2">
-        <v>55.8</v>
+        <v>58.1</v>
       </c>
       <c r="L2" t="s">
         <v>26</v>
@@ -549,7 +549,7 @@
         <v>27</v>
       </c>
       <c r="N2">
-        <v>48.11568981226033</v>
+        <v>46.17217538625081</v>
       </c>
       <c r="O2" t="s">
         <v>28</v>
@@ -566,28 +566,28 @@
         <v>22</v>
       </c>
       <c r="D3">
-        <v>303.93</v>
+        <v>184.97</v>
       </c>
       <c r="E3">
-        <v>74.40000000000001</v>
+        <v>54.3</v>
       </c>
       <c r="F3">
-        <v>4.05</v>
+        <v>1.94</v>
       </c>
       <c r="G3">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="H3">
+        <v>63</v>
+      </c>
+      <c r="I3">
         <v>66</v>
       </c>
-      <c r="I3">
-        <v>73</v>
-      </c>
       <c r="J3">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="K3">
-        <v>55.6</v>
+        <v>55.3</v>
       </c>
       <c r="L3" t="s">
         <v>26</v>
@@ -596,7 +596,7 @@
         <v>27</v>
       </c>
       <c r="N3">
-        <v>48.11568981226033</v>
+        <v>46.17217538625081</v>
       </c>
       <c r="O3" t="s">
         <v>28</v>
@@ -613,13 +613,13 @@
         <v>23</v>
       </c>
       <c r="D4">
-        <v>1110.97</v>
+        <v>1111.44</v>
       </c>
       <c r="E4">
         <v>65.2</v>
       </c>
       <c r="F4">
-        <v>0.2</v>
+        <v>0.24</v>
       </c>
       <c r="G4">
         <v>60</v>
@@ -634,7 +634,7 @@
         <v>56</v>
       </c>
       <c r="K4">
-        <v>54.8</v>
+        <v>54.3</v>
       </c>
       <c r="L4" t="s">
         <v>26</v>
@@ -643,7 +643,7 @@
         <v>27</v>
       </c>
       <c r="N4">
-        <v>48.11568981226033</v>
+        <v>46.17217538625081</v>
       </c>
       <c r="O4" t="s">
         <v>28</v>
@@ -660,13 +660,13 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>222.65</v>
+        <v>221.62</v>
       </c>
       <c r="E5">
-        <v>44.9</v>
+        <v>44.2</v>
       </c>
       <c r="F5">
-        <v>3.44</v>
+        <v>2.96</v>
       </c>
       <c r="G5">
         <v>30</v>
@@ -681,7 +681,7 @@
         <v>70</v>
       </c>
       <c r="K5">
-        <v>51.4</v>
+        <v>50.9</v>
       </c>
       <c r="L5" t="s">
         <v>26</v>
@@ -690,7 +690,7 @@
         <v>27</v>
       </c>
       <c r="N5">
-        <v>48.11568981226033</v>
+        <v>46.17217538625081</v>
       </c>
       <c r="O5" t="s">
         <v>28</v>
@@ -707,13 +707,13 @@
         <v>25</v>
       </c>
       <c r="D6">
-        <v>175.54</v>
+        <v>176</v>
       </c>
       <c r="E6">
-        <v>70.3</v>
+        <v>70.8</v>
       </c>
       <c r="F6">
-        <v>3.36</v>
+        <v>3.63</v>
       </c>
       <c r="G6">
         <v>50</v>
@@ -728,7 +728,7 @@
         <v>43</v>
       </c>
       <c r="K6">
-        <v>43.8</v>
+        <v>43.3</v>
       </c>
       <c r="L6" t="s">
         <v>26</v>
@@ -737,7 +737,7 @@
         <v>27</v>
       </c>
       <c r="N6">
-        <v>48.11568981226033</v>
+        <v>46.17217538625081</v>
       </c>
       <c r="O6" t="s">
         <v>28</v>

--- a/DECISION/미장_반도체_분석.xlsx
+++ b/DECISION/미장_반도체_분석.xlsx
@@ -61,7 +61,7 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2025-12-10</t>
+    <t>2025-12-15</t>
   </si>
   <si>
     <t>Taiwan Semiconductor Manufactur</t>
@@ -70,28 +70,28 @@
     <t>NVIDIA Corporation</t>
   </si>
   <si>
+    <t>QUALCOMM Incorporated</t>
+  </si>
+  <si>
     <t>ASML Holding N.V. - New York Re</t>
   </si>
   <si>
     <t>Advanced Micro Devices, Inc.</t>
   </si>
   <si>
-    <t>QUALCOMM Incorporated</t>
-  </si>
-  <si>
     <t>TSM</t>
   </si>
   <si>
     <t>NVDA</t>
   </si>
   <si>
+    <t>QCOM</t>
+  </si>
+  <si>
     <t>ASML</t>
   </si>
   <si>
     <t>AMD</t>
-  </si>
-  <si>
-    <t>QCOM</t>
   </si>
   <si>
     <t>Pattern</t>
@@ -519,28 +519,28 @@
         <v>21</v>
       </c>
       <c r="D2">
-        <v>303.41</v>
+        <v>292.04</v>
       </c>
       <c r="E2">
-        <v>74.09999999999999</v>
+        <v>63.6</v>
       </c>
       <c r="F2">
-        <v>3.88</v>
+        <v>-0.64</v>
       </c>
       <c r="G2">
         <v>50</v>
       </c>
       <c r="H2">
+        <v>63</v>
+      </c>
+      <c r="I2">
         <v>66</v>
-      </c>
-      <c r="I2">
-        <v>73</v>
       </c>
       <c r="J2">
         <v>86</v>
       </c>
       <c r="K2">
-        <v>58.1</v>
+        <v>55.6</v>
       </c>
       <c r="L2" t="s">
         <v>26</v>
@@ -549,7 +549,7 @@
         <v>27</v>
       </c>
       <c r="N2">
-        <v>46.17217538625081</v>
+        <v>47.37006702605126</v>
       </c>
       <c r="O2" t="s">
         <v>28</v>
@@ -566,28 +566,28 @@
         <v>22</v>
       </c>
       <c r="D3">
-        <v>184.97</v>
+        <v>175.02</v>
       </c>
       <c r="E3">
-        <v>54.3</v>
+        <v>45</v>
       </c>
       <c r="F3">
-        <v>1.94</v>
+        <v>-4.05</v>
       </c>
       <c r="G3">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H3">
+        <v>60</v>
+      </c>
+      <c r="I3">
         <v>63</v>
       </c>
-      <c r="I3">
-        <v>66</v>
-      </c>
       <c r="J3">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="K3">
-        <v>55.3</v>
+        <v>48.4</v>
       </c>
       <c r="L3" t="s">
         <v>26</v>
@@ -596,7 +596,7 @@
         <v>27</v>
       </c>
       <c r="N3">
-        <v>46.17217538625081</v>
+        <v>47.37006702605126</v>
       </c>
       <c r="O3" t="s">
         <v>28</v>
@@ -613,28 +613,28 @@
         <v>23</v>
       </c>
       <c r="D4">
-        <v>1111.44</v>
+        <v>178.29</v>
       </c>
       <c r="E4">
-        <v>65.2</v>
+        <v>79</v>
       </c>
       <c r="F4">
-        <v>0.24</v>
+        <v>1.99</v>
       </c>
       <c r="G4">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H4">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="I4">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="J4">
         <v>56</v>
       </c>
       <c r="K4">
-        <v>54.3</v>
+        <v>47.6</v>
       </c>
       <c r="L4" t="s">
         <v>26</v>
@@ -643,7 +643,7 @@
         <v>27</v>
       </c>
       <c r="N4">
-        <v>46.17217538625081</v>
+        <v>47.37006702605126</v>
       </c>
       <c r="O4" t="s">
         <v>28</v>
@@ -660,28 +660,28 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>221.62</v>
+        <v>1080.85</v>
       </c>
       <c r="E5">
-        <v>44.2</v>
+        <v>69.2</v>
       </c>
       <c r="F5">
-        <v>2.96</v>
+        <v>-1.69</v>
       </c>
       <c r="G5">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="H5">
+        <v>43</v>
+      </c>
+      <c r="I5">
+        <v>46</v>
+      </c>
+      <c r="J5">
         <v>73</v>
       </c>
-      <c r="I5">
-        <v>70</v>
-      </c>
-      <c r="J5">
-        <v>70</v>
-      </c>
       <c r="K5">
-        <v>50.9</v>
+        <v>47.6</v>
       </c>
       <c r="L5" t="s">
         <v>26</v>
@@ -690,7 +690,7 @@
         <v>27</v>
       </c>
       <c r="N5">
-        <v>46.17217538625081</v>
+        <v>47.37006702605126</v>
       </c>
       <c r="O5" t="s">
         <v>28</v>
@@ -707,28 +707,28 @@
         <v>25</v>
       </c>
       <c r="D6">
-        <v>176</v>
+        <v>210.78</v>
       </c>
       <c r="E6">
-        <v>70.8</v>
+        <v>56</v>
       </c>
       <c r="F6">
-        <v>3.63</v>
+        <v>-3.3</v>
       </c>
       <c r="G6">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H6">
-        <v>40</v>
+        <v>76</v>
       </c>
       <c r="I6">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="J6">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="K6">
-        <v>43.3</v>
+        <v>45.4</v>
       </c>
       <c r="L6" t="s">
         <v>26</v>
@@ -737,7 +737,7 @@
         <v>27</v>
       </c>
       <c r="N6">
-        <v>46.17217538625081</v>
+        <v>47.37006702605126</v>
       </c>
       <c r="O6" t="s">
         <v>28</v>

--- a/DECISION/미장_반도체_분석.xlsx
+++ b/DECISION/미장_반도체_분석.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="30">
   <si>
     <t>날짜</t>
   </si>
@@ -61,40 +61,43 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2025-12-15</t>
+    <t>2025-12-29</t>
+  </si>
+  <si>
+    <t>NVIDIA Corporation</t>
   </si>
   <si>
     <t>Taiwan Semiconductor Manufactur</t>
   </si>
   <si>
-    <t>NVIDIA Corporation</t>
+    <t>Advanced Micro Devices, Inc.</t>
+  </si>
+  <si>
+    <t>ASML Holding N.V. - New York Re</t>
   </si>
   <si>
     <t>QUALCOMM Incorporated</t>
   </si>
   <si>
-    <t>ASML Holding N.V. - New York Re</t>
-  </si>
-  <si>
-    <t>Advanced Micro Devices, Inc.</t>
+    <t>NVDA</t>
   </si>
   <si>
     <t>TSM</t>
   </si>
   <si>
-    <t>NVDA</t>
+    <t>AMD</t>
+  </si>
+  <si>
+    <t>ASML</t>
   </si>
   <si>
     <t>QCOM</t>
   </si>
   <si>
-    <t>ASML</t>
-  </si>
-  <si>
-    <t>AMD</t>
-  </si>
-  <si>
     <t>Pattern</t>
+  </si>
+  <si>
+    <t>📈 매수 관찰 구간입니다.</t>
   </si>
   <si>
     <t>⛔ 관망하십시오.</t>
@@ -519,28 +522,28 @@
         <v>21</v>
       </c>
       <c r="D2">
-        <v>292.04</v>
+        <v>190.53</v>
       </c>
       <c r="E2">
-        <v>63.6</v>
+        <v>59.2</v>
       </c>
       <c r="F2">
-        <v>-0.64</v>
+        <v>9.41</v>
       </c>
       <c r="G2">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H2">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="I2">
+        <v>70</v>
+      </c>
+      <c r="J2">
         <v>66</v>
       </c>
-      <c r="J2">
-        <v>86</v>
-      </c>
       <c r="K2">
-        <v>55.6</v>
+        <v>61.6</v>
       </c>
       <c r="L2" t="s">
         <v>26</v>
@@ -549,10 +552,10 @@
         <v>27</v>
       </c>
       <c r="N2">
-        <v>47.37006702605126</v>
+        <v>51.940834218365</v>
       </c>
       <c r="O2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -566,28 +569,28 @@
         <v>22</v>
       </c>
       <c r="D3">
-        <v>175.02</v>
+        <v>302.84</v>
       </c>
       <c r="E3">
-        <v>45</v>
+        <v>56.1</v>
       </c>
       <c r="F3">
-        <v>-4.05</v>
+        <v>6.38</v>
       </c>
       <c r="G3">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="H3">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="I3">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="J3">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="K3">
-        <v>48.4</v>
+        <v>61.6</v>
       </c>
       <c r="L3" t="s">
         <v>26</v>
@@ -596,10 +599,10 @@
         <v>27</v>
       </c>
       <c r="N3">
-        <v>47.37006702605126</v>
+        <v>51.940834218365</v>
       </c>
       <c r="O3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -613,40 +616,40 @@
         <v>23</v>
       </c>
       <c r="D4">
-        <v>178.29</v>
+        <v>214.99</v>
       </c>
       <c r="E4">
-        <v>79</v>
+        <v>46.9</v>
       </c>
       <c r="F4">
-        <v>1.99</v>
+        <v>6.93</v>
       </c>
       <c r="G4">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H4">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="I4">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="J4">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="K4">
-        <v>47.6</v>
+        <v>60</v>
       </c>
       <c r="L4" t="s">
         <v>26</v>
       </c>
       <c r="M4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="N4">
-        <v>47.37006702605126</v>
+        <v>51.940834218365</v>
       </c>
       <c r="O4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -660,40 +663,40 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>1080.85</v>
+        <v>1072.75</v>
       </c>
       <c r="E5">
-        <v>69.2</v>
+        <v>43.9</v>
       </c>
       <c r="F5">
-        <v>-1.69</v>
+        <v>3.52</v>
       </c>
       <c r="G5">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H5">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="I5">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="J5">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="K5">
-        <v>47.6</v>
+        <v>47</v>
       </c>
       <c r="L5" t="s">
         <v>26</v>
       </c>
       <c r="M5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="N5">
-        <v>47.37006702605126</v>
+        <v>51.940834218365</v>
       </c>
       <c r="O5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:15">
@@ -707,40 +710,40 @@
         <v>25</v>
       </c>
       <c r="D6">
-        <v>210.78</v>
+        <v>174.81</v>
       </c>
       <c r="E6">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="F6">
-        <v>-3.3</v>
+        <v>0.36</v>
       </c>
       <c r="G6">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H6">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="I6">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="J6">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="K6">
-        <v>45.4</v>
+        <v>44.6</v>
       </c>
       <c r="L6" t="s">
         <v>26</v>
       </c>
       <c r="M6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="N6">
-        <v>47.37006702605126</v>
+        <v>51.940834218365</v>
       </c>
       <c r="O6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/DECISION/미장_반도체_분석.xlsx
+++ b/DECISION/미장_반도체_분석.xlsx
@@ -61,34 +61,34 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2025-12-29</t>
+    <t>2026-01-05</t>
+  </si>
+  <si>
+    <t>Advanced Micro Devices, Inc.</t>
   </si>
   <si>
     <t>NVIDIA Corporation</t>
   </si>
   <si>
+    <t>ASML Holding N.V. - New York Re</t>
+  </si>
+  <si>
     <t>Taiwan Semiconductor Manufactur</t>
   </si>
   <si>
-    <t>Advanced Micro Devices, Inc.</t>
-  </si>
-  <si>
-    <t>ASML Holding N.V. - New York Re</t>
-  </si>
-  <si>
     <t>QUALCOMM Incorporated</t>
   </si>
   <si>
+    <t>AMD</t>
+  </si>
+  <si>
     <t>NVDA</t>
   </si>
   <si>
+    <t>ASML</t>
+  </si>
+  <si>
     <t>TSM</t>
-  </si>
-  <si>
-    <t>AMD</t>
-  </si>
-  <si>
-    <t>ASML</t>
   </si>
   <si>
     <t>QCOM</t>
@@ -522,28 +522,28 @@
         <v>21</v>
       </c>
       <c r="D2">
-        <v>190.53</v>
+        <v>223.47</v>
       </c>
       <c r="E2">
-        <v>59.2</v>
+        <v>51.9</v>
       </c>
       <c r="F2">
-        <v>9.41</v>
+        <v>3.92</v>
       </c>
       <c r="G2">
         <v>60</v>
       </c>
       <c r="H2">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="I2">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="J2">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="K2">
-        <v>61.6</v>
+        <v>62.5</v>
       </c>
       <c r="L2" t="s">
         <v>26</v>
@@ -552,7 +552,7 @@
         <v>27</v>
       </c>
       <c r="N2">
-        <v>51.940834218365</v>
+        <v>41.50472307187444</v>
       </c>
       <c r="O2" t="s">
         <v>29</v>
@@ -569,37 +569,37 @@
         <v>22</v>
       </c>
       <c r="D3">
-        <v>302.84</v>
+        <v>188.85</v>
       </c>
       <c r="E3">
-        <v>56.1</v>
+        <v>59.3</v>
       </c>
       <c r="F3">
-        <v>6.38</v>
+        <v>0.13</v>
       </c>
       <c r="G3">
         <v>60</v>
       </c>
       <c r="H3">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="I3">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="J3">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="K3">
-        <v>61.6</v>
+        <v>56.9</v>
       </c>
       <c r="L3" t="s">
         <v>26</v>
       </c>
       <c r="M3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="N3">
-        <v>51.940834218365</v>
+        <v>41.50472307187444</v>
       </c>
       <c r="O3" t="s">
         <v>29</v>
@@ -616,28 +616,28 @@
         <v>23</v>
       </c>
       <c r="D4">
-        <v>214.99</v>
+        <v>1163.78</v>
       </c>
       <c r="E4">
-        <v>46.9</v>
+        <v>57.1</v>
       </c>
       <c r="F4">
-        <v>6.93</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="G4">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H4">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="I4">
+        <v>70</v>
+      </c>
+      <c r="J4">
         <v>66</v>
       </c>
-      <c r="J4">
-        <v>70</v>
-      </c>
       <c r="K4">
-        <v>60</v>
+        <v>55.5</v>
       </c>
       <c r="L4" t="s">
         <v>26</v>
@@ -646,7 +646,7 @@
         <v>28</v>
       </c>
       <c r="N4">
-        <v>51.940834218365</v>
+        <v>41.50472307187444</v>
       </c>
       <c r="O4" t="s">
         <v>29</v>
@@ -663,28 +663,28 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>1072.75</v>
+        <v>319.61</v>
       </c>
       <c r="E5">
-        <v>43.9</v>
+        <v>59.6</v>
       </c>
       <c r="F5">
-        <v>3.52</v>
+        <v>6.96</v>
       </c>
       <c r="G5">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="H5">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="I5">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="J5">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="K5">
-        <v>47</v>
+        <v>53.9</v>
       </c>
       <c r="L5" t="s">
         <v>26</v>
@@ -693,7 +693,7 @@
         <v>28</v>
       </c>
       <c r="N5">
-        <v>51.940834218365</v>
+        <v>41.50472307187444</v>
       </c>
       <c r="O5" t="s">
         <v>29</v>
@@ -710,28 +710,28 @@
         <v>25</v>
       </c>
       <c r="D6">
-        <v>174.81</v>
+        <v>172.98</v>
       </c>
       <c r="E6">
-        <v>50</v>
+        <v>30.7</v>
       </c>
       <c r="F6">
-        <v>0.36</v>
+        <v>-1.02</v>
       </c>
       <c r="G6">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="H6">
         <v>53</v>
       </c>
       <c r="I6">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="J6">
         <v>46</v>
       </c>
       <c r="K6">
-        <v>44.6</v>
+        <v>36.7</v>
       </c>
       <c r="L6" t="s">
         <v>26</v>
@@ -740,7 +740,7 @@
         <v>28</v>
       </c>
       <c r="N6">
-        <v>51.940834218365</v>
+        <v>41.50472307187444</v>
       </c>
       <c r="O6" t="s">
         <v>29</v>

--- a/DECISION/미장_반도체_분석.xlsx
+++ b/DECISION/미장_반도체_분석.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="29">
   <si>
     <t>날짜</t>
   </si>
@@ -61,43 +61,40 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-01-05</t>
+    <t>2026-01-07</t>
+  </si>
+  <si>
+    <t>NVIDIA Corporation</t>
   </si>
   <si>
     <t>Advanced Micro Devices, Inc.</t>
   </si>
   <si>
-    <t>NVIDIA Corporation</t>
+    <t>Taiwan Semiconductor Manufactur</t>
   </si>
   <si>
     <t>ASML Holding N.V. - New York Re</t>
   </si>
   <si>
-    <t>Taiwan Semiconductor Manufactur</t>
-  </si>
-  <si>
     <t>QUALCOMM Incorporated</t>
   </si>
   <si>
+    <t>NVDA</t>
+  </si>
+  <si>
     <t>AMD</t>
   </si>
   <si>
-    <t>NVDA</t>
+    <t>TSM</t>
   </si>
   <si>
     <t>ASML</t>
   </si>
   <si>
-    <t>TSM</t>
-  </si>
-  <si>
     <t>QCOM</t>
   </si>
   <si>
     <t>Pattern</t>
-  </si>
-  <si>
-    <t>📈 매수 관찰 구간입니다.</t>
   </si>
   <si>
     <t>⛔ 관망하십시오.</t>
@@ -522,28 +519,28 @@
         <v>21</v>
       </c>
       <c r="D2">
-        <v>223.47</v>
+        <v>187.24</v>
       </c>
       <c r="E2">
-        <v>51.9</v>
+        <v>64.8</v>
       </c>
       <c r="F2">
-        <v>3.92</v>
+        <v>-0.52</v>
       </c>
       <c r="G2">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H2">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="I2">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="J2">
         <v>73</v>
       </c>
       <c r="K2">
-        <v>62.5</v>
+        <v>57.7</v>
       </c>
       <c r="L2" t="s">
         <v>26</v>
@@ -552,10 +549,10 @@
         <v>27</v>
       </c>
       <c r="N2">
-        <v>41.50472307187444</v>
+        <v>45.04298008974126</v>
       </c>
       <c r="O2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -569,40 +566,40 @@
         <v>22</v>
       </c>
       <c r="D3">
-        <v>188.85</v>
+        <v>214.35</v>
       </c>
       <c r="E3">
-        <v>59.3</v>
+        <v>56.7</v>
       </c>
       <c r="F3">
-        <v>0.13</v>
+        <v>-0.58</v>
       </c>
       <c r="G3">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="H3">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="I3">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="J3">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="K3">
-        <v>56.9</v>
+        <v>55.9</v>
       </c>
       <c r="L3" t="s">
         <v>26</v>
       </c>
       <c r="M3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N3">
+        <v>45.04298008974126</v>
+      </c>
+      <c r="O3" t="s">
         <v>28</v>
-      </c>
-      <c r="N3">
-        <v>41.50472307187444</v>
-      </c>
-      <c r="O3" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -616,40 +613,40 @@
         <v>23</v>
       </c>
       <c r="D4">
-        <v>1163.78</v>
+        <v>327.43</v>
       </c>
       <c r="E4">
-        <v>57.1</v>
+        <v>79.3</v>
       </c>
       <c r="F4">
-        <v>9.220000000000001</v>
+        <v>8.81</v>
       </c>
       <c r="G4">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H4">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="I4">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="J4">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="K4">
-        <v>55.5</v>
+        <v>50.7</v>
       </c>
       <c r="L4" t="s">
         <v>26</v>
       </c>
       <c r="M4" t="s">
+        <v>27</v>
+      </c>
+      <c r="N4">
+        <v>45.04298008974126</v>
+      </c>
+      <c r="O4" t="s">
         <v>28</v>
-      </c>
-      <c r="N4">
-        <v>41.50472307187444</v>
-      </c>
-      <c r="O4" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -663,40 +660,40 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>319.61</v>
+        <v>1242.19</v>
       </c>
       <c r="E5">
-        <v>59.6</v>
+        <v>74.3</v>
       </c>
       <c r="F5">
-        <v>6.96</v>
+        <v>16.53</v>
       </c>
       <c r="G5">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H5">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="I5">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="J5">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="K5">
-        <v>53.9</v>
+        <v>46.7</v>
       </c>
       <c r="L5" t="s">
         <v>26</v>
       </c>
       <c r="M5" t="s">
+        <v>27</v>
+      </c>
+      <c r="N5">
+        <v>45.04298008974126</v>
+      </c>
+      <c r="O5" t="s">
         <v>28</v>
-      </c>
-      <c r="N5">
-        <v>41.50472307187444</v>
-      </c>
-      <c r="O5" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:15">
@@ -710,40 +707,40 @@
         <v>25</v>
       </c>
       <c r="D6">
-        <v>172.98</v>
+        <v>182.45</v>
       </c>
       <c r="E6">
-        <v>30.7</v>
+        <v>55.9</v>
       </c>
       <c r="F6">
-        <v>-1.02</v>
+        <v>5.2</v>
       </c>
       <c r="G6">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="H6">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="I6">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="J6">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="K6">
-        <v>36.7</v>
+        <v>42.7</v>
       </c>
       <c r="L6" t="s">
         <v>26</v>
       </c>
       <c r="M6" t="s">
+        <v>27</v>
+      </c>
+      <c r="N6">
+        <v>45.04298008974126</v>
+      </c>
+      <c r="O6" t="s">
         <v>28</v>
-      </c>
-      <c r="N6">
-        <v>41.50472307187444</v>
-      </c>
-      <c r="O6" t="s">
-        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/DECISION/미장_반도체_분석.xlsx
+++ b/DECISION/미장_반도체_분석.xlsx
@@ -540,7 +540,7 @@
         <v>73</v>
       </c>
       <c r="K2">
-        <v>57.7</v>
+        <v>57.8</v>
       </c>
       <c r="L2" t="s">
         <v>26</v>
@@ -549,7 +549,7 @@
         <v>27</v>
       </c>
       <c r="N2">
-        <v>45.04298008974126</v>
+        <v>45.26531441048893</v>
       </c>
       <c r="O2" t="s">
         <v>28</v>
@@ -587,7 +587,7 @@
         <v>76</v>
       </c>
       <c r="K3">
-        <v>55.9</v>
+        <v>56</v>
       </c>
       <c r="L3" t="s">
         <v>26</v>
@@ -596,7 +596,7 @@
         <v>27</v>
       </c>
       <c r="N3">
-        <v>45.04298008974126</v>
+        <v>45.26531441048893</v>
       </c>
       <c r="O3" t="s">
         <v>28</v>
@@ -634,7 +634,7 @@
         <v>83</v>
       </c>
       <c r="K4">
-        <v>50.7</v>
+        <v>50.8</v>
       </c>
       <c r="L4" t="s">
         <v>26</v>
@@ -643,7 +643,7 @@
         <v>27</v>
       </c>
       <c r="N4">
-        <v>45.04298008974126</v>
+        <v>45.26531441048893</v>
       </c>
       <c r="O4" t="s">
         <v>28</v>
@@ -681,7 +681,7 @@
         <v>70</v>
       </c>
       <c r="K5">
-        <v>46.7</v>
+        <v>46.8</v>
       </c>
       <c r="L5" t="s">
         <v>26</v>
@@ -690,7 +690,7 @@
         <v>27</v>
       </c>
       <c r="N5">
-        <v>45.04298008974126</v>
+        <v>45.26531441048893</v>
       </c>
       <c r="O5" t="s">
         <v>28</v>
@@ -728,7 +728,7 @@
         <v>40</v>
       </c>
       <c r="K6">
-        <v>42.7</v>
+        <v>42.8</v>
       </c>
       <c r="L6" t="s">
         <v>26</v>
@@ -737,7 +737,7 @@
         <v>27</v>
       </c>
       <c r="N6">
-        <v>45.04298008974126</v>
+        <v>45.26531441048893</v>
       </c>
       <c r="O6" t="s">
         <v>28</v>

--- a/DECISION/미장_반도체_분석.xlsx
+++ b/DECISION/미장_반도체_분석.xlsx
@@ -61,18 +61,18 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-01-07</t>
+    <t>2026-01-08</t>
   </si>
   <si>
     <t>NVIDIA Corporation</t>
   </si>
   <si>
+    <t>Taiwan Semiconductor Manufactur</t>
+  </si>
+  <si>
     <t>Advanced Micro Devices, Inc.</t>
   </si>
   <si>
-    <t>Taiwan Semiconductor Manufactur</t>
-  </si>
-  <si>
     <t>ASML Holding N.V. - New York Re</t>
   </si>
   <si>
@@ -82,10 +82,10 @@
     <t>NVDA</t>
   </si>
   <si>
+    <t>TSM</t>
+  </si>
+  <si>
     <t>AMD</t>
-  </si>
-  <si>
-    <t>TSM</t>
   </si>
   <si>
     <t>ASML</t>
@@ -519,28 +519,28 @@
         <v>21</v>
       </c>
       <c r="D2">
-        <v>187.24</v>
+        <v>189.11</v>
       </c>
       <c r="E2">
-        <v>64.8</v>
+        <v>65.2</v>
       </c>
       <c r="F2">
-        <v>-0.52</v>
+        <v>0.84</v>
       </c>
       <c r="G2">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H2">
         <v>76</v>
       </c>
       <c r="I2">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="J2">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="K2">
-        <v>57.8</v>
+        <v>59.1</v>
       </c>
       <c r="L2" t="s">
         <v>26</v>
@@ -549,7 +549,7 @@
         <v>27</v>
       </c>
       <c r="N2">
-        <v>45.26531441048893</v>
+        <v>43.60821037092016</v>
       </c>
       <c r="O2" t="s">
         <v>28</v>
@@ -566,28 +566,28 @@
         <v>22</v>
       </c>
       <c r="D3">
-        <v>214.35</v>
+        <v>318.68</v>
       </c>
       <c r="E3">
-        <v>56.7</v>
+        <v>71</v>
       </c>
       <c r="F3">
-        <v>-0.58</v>
+        <v>6.38</v>
       </c>
       <c r="G3">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="H3">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="I3">
         <v>76</v>
       </c>
       <c r="J3">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="K3">
-        <v>56</v>
+        <v>58.5</v>
       </c>
       <c r="L3" t="s">
         <v>26</v>
@@ -596,7 +596,7 @@
         <v>27</v>
       </c>
       <c r="N3">
-        <v>45.26531441048893</v>
+        <v>43.60821037092016</v>
       </c>
       <c r="O3" t="s">
         <v>28</v>
@@ -613,28 +613,28 @@
         <v>23</v>
       </c>
       <c r="D4">
-        <v>327.43</v>
+        <v>210.02</v>
       </c>
       <c r="E4">
-        <v>79.3</v>
+        <v>50.8</v>
       </c>
       <c r="F4">
-        <v>8.81</v>
+        <v>-2.47</v>
       </c>
       <c r="G4">
         <v>40</v>
       </c>
       <c r="H4">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="I4">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="J4">
         <v>83</v>
       </c>
       <c r="K4">
-        <v>50.8</v>
+        <v>54.3</v>
       </c>
       <c r="L4" t="s">
         <v>26</v>
@@ -643,7 +643,7 @@
         <v>27</v>
       </c>
       <c r="N4">
-        <v>45.26531441048893</v>
+        <v>43.60821037092016</v>
       </c>
       <c r="O4" t="s">
         <v>28</v>
@@ -660,28 +660,28 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>1242.19</v>
+        <v>1228.47</v>
       </c>
       <c r="E5">
-        <v>74.3</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="F5">
-        <v>16.53</v>
+        <v>14.58</v>
       </c>
       <c r="G5">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="H5">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="I5">
         <v>53</v>
       </c>
       <c r="J5">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="K5">
-        <v>46.8</v>
+        <v>49.3</v>
       </c>
       <c r="L5" t="s">
         <v>26</v>
@@ -690,7 +690,7 @@
         <v>27</v>
       </c>
       <c r="N5">
-        <v>45.26531441048893</v>
+        <v>43.60821037092016</v>
       </c>
       <c r="O5" t="s">
         <v>28</v>
@@ -707,28 +707,28 @@
         <v>25</v>
       </c>
       <c r="D6">
-        <v>182.45</v>
+        <v>180.19</v>
       </c>
       <c r="E6">
-        <v>55.9</v>
+        <v>57.8</v>
       </c>
       <c r="F6">
-        <v>5.2</v>
+        <v>3.77</v>
       </c>
       <c r="G6">
+        <v>60</v>
+      </c>
+      <c r="H6">
+        <v>50</v>
+      </c>
+      <c r="I6">
         <v>40</v>
       </c>
-      <c r="H6">
+      <c r="J6">
         <v>46</v>
       </c>
-      <c r="I6">
-        <v>43</v>
-      </c>
-      <c r="J6">
-        <v>40</v>
-      </c>
       <c r="K6">
-        <v>42.8</v>
+        <v>47.1</v>
       </c>
       <c r="L6" t="s">
         <v>26</v>
@@ -737,7 +737,7 @@
         <v>27</v>
       </c>
       <c r="N6">
-        <v>45.26531441048893</v>
+        <v>43.60821037092016</v>
       </c>
       <c r="O6" t="s">
         <v>28</v>

--- a/DECISION/미장_반도체_분석.xlsx
+++ b/DECISION/미장_반도체_분석.xlsx
@@ -61,37 +61,37 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-01-08</t>
+    <t>2026-01-11</t>
+  </si>
+  <si>
+    <t>Taiwan Semiconductor Manufactur</t>
+  </si>
+  <si>
+    <t>QUALCOMM Incorporated</t>
   </si>
   <si>
     <t>NVIDIA Corporation</t>
   </si>
   <si>
-    <t>Taiwan Semiconductor Manufactur</t>
-  </si>
-  <si>
     <t>Advanced Micro Devices, Inc.</t>
   </si>
   <si>
     <t>ASML Holding N.V. - New York Re</t>
   </si>
   <si>
-    <t>QUALCOMM Incorporated</t>
+    <t>TSM</t>
+  </si>
+  <si>
+    <t>QCOM</t>
   </si>
   <si>
     <t>NVDA</t>
   </si>
   <si>
-    <t>TSM</t>
-  </si>
-  <si>
     <t>AMD</t>
   </si>
   <si>
     <t>ASML</t>
-  </si>
-  <si>
-    <t>QCOM</t>
   </si>
   <si>
     <t>Pattern</t>
@@ -519,28 +519,28 @@
         <v>21</v>
       </c>
       <c r="D2">
-        <v>189.11</v>
+        <v>323.63</v>
       </c>
       <c r="E2">
-        <v>65.2</v>
+        <v>80.3</v>
       </c>
       <c r="F2">
-        <v>0.84</v>
+        <v>1.26</v>
       </c>
       <c r="G2">
+        <v>50</v>
+      </c>
+      <c r="H2">
         <v>60</v>
       </c>
-      <c r="H2">
-        <v>76</v>
-      </c>
       <c r="I2">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="J2">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="K2">
-        <v>59.1</v>
+        <v>56.5</v>
       </c>
       <c r="L2" t="s">
         <v>26</v>
@@ -549,7 +549,7 @@
         <v>27</v>
       </c>
       <c r="N2">
-        <v>43.60821037092016</v>
+        <v>50.40292622392195</v>
       </c>
       <c r="O2" t="s">
         <v>28</v>
@@ -566,28 +566,28 @@
         <v>22</v>
       </c>
       <c r="D3">
-        <v>318.68</v>
+        <v>177.78</v>
       </c>
       <c r="E3">
-        <v>71</v>
+        <v>56.8</v>
       </c>
       <c r="F3">
-        <v>6.38</v>
+        <v>2.77</v>
       </c>
       <c r="G3">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H3">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="I3">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="J3">
-        <v>80</v>
+        <v>53</v>
       </c>
       <c r="K3">
-        <v>58.5</v>
+        <v>54.3</v>
       </c>
       <c r="L3" t="s">
         <v>26</v>
@@ -596,7 +596,7 @@
         <v>27</v>
       </c>
       <c r="N3">
-        <v>43.60821037092016</v>
+        <v>50.40292622392195</v>
       </c>
       <c r="O3" t="s">
         <v>28</v>
@@ -613,28 +613,28 @@
         <v>23</v>
       </c>
       <c r="D4">
-        <v>210.02</v>
+        <v>184.86</v>
       </c>
       <c r="E4">
-        <v>50.8</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="F4">
-        <v>-2.47</v>
+        <v>-2.11</v>
       </c>
       <c r="G4">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="H4">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="I4">
+        <v>53</v>
+      </c>
+      <c r="J4">
         <v>73</v>
       </c>
-      <c r="J4">
-        <v>83</v>
-      </c>
       <c r="K4">
-        <v>54.3</v>
+        <v>51.3</v>
       </c>
       <c r="L4" t="s">
         <v>26</v>
@@ -643,7 +643,7 @@
         <v>27</v>
       </c>
       <c r="N4">
-        <v>43.60821037092016</v>
+        <v>50.40292622392195</v>
       </c>
       <c r="O4" t="s">
         <v>28</v>
@@ -660,28 +660,28 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>1228.47</v>
+        <v>203.17</v>
       </c>
       <c r="E5">
-        <v>73.90000000000001</v>
+        <v>52.3</v>
       </c>
       <c r="F5">
-        <v>14.58</v>
+        <v>-9.08</v>
       </c>
       <c r="G5">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H5">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="I5">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="J5">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="K5">
-        <v>49.3</v>
+        <v>50.3</v>
       </c>
       <c r="L5" t="s">
         <v>26</v>
@@ -690,7 +690,7 @@
         <v>27</v>
       </c>
       <c r="N5">
-        <v>43.60821037092016</v>
+        <v>50.40292622392195</v>
       </c>
       <c r="O5" t="s">
         <v>28</v>
@@ -707,28 +707,28 @@
         <v>25</v>
       </c>
       <c r="D6">
-        <v>180.19</v>
+        <v>1273.88</v>
       </c>
       <c r="E6">
-        <v>57.8</v>
+        <v>83.8</v>
       </c>
       <c r="F6">
-        <v>3.77</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="G6">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="H6">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="I6">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="J6">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="K6">
-        <v>47.1</v>
+        <v>49.5</v>
       </c>
       <c r="L6" t="s">
         <v>26</v>
@@ -737,7 +737,7 @@
         <v>27</v>
       </c>
       <c r="N6">
-        <v>43.60821037092016</v>
+        <v>50.40292622392195</v>
       </c>
       <c r="O6" t="s">
         <v>28</v>

--- a/DECISION/미장_반도체_분석.xlsx
+++ b/DECISION/미장_반도체_분석.xlsx
@@ -61,7 +61,7 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-01-11</t>
+    <t>2026-01-12</t>
   </si>
   <si>
     <t>Taiwan Semiconductor Manufactur</t>
@@ -549,7 +549,7 @@
         <v>27</v>
       </c>
       <c r="N2">
-        <v>50.40292622392195</v>
+        <v>50.43822221555986</v>
       </c>
       <c r="O2" t="s">
         <v>28</v>
@@ -596,7 +596,7 @@
         <v>27</v>
       </c>
       <c r="N3">
-        <v>50.40292622392195</v>
+        <v>50.43822221555986</v>
       </c>
       <c r="O3" t="s">
         <v>28</v>
@@ -643,7 +643,7 @@
         <v>27</v>
       </c>
       <c r="N4">
-        <v>50.40292622392195</v>
+        <v>50.43822221555986</v>
       </c>
       <c r="O4" t="s">
         <v>28</v>
@@ -690,7 +690,7 @@
         <v>27</v>
       </c>
       <c r="N5">
-        <v>50.40292622392195</v>
+        <v>50.43822221555986</v>
       </c>
       <c r="O5" t="s">
         <v>28</v>
@@ -737,7 +737,7 @@
         <v>27</v>
       </c>
       <c r="N6">
-        <v>50.40292622392195</v>
+        <v>50.43822221555986</v>
       </c>
       <c r="O6" t="s">
         <v>28</v>

--- a/DECISION/미장_반도체_분석.xlsx
+++ b/DECISION/미장_반도체_분석.xlsx
@@ -540,7 +540,7 @@
         <v>83</v>
       </c>
       <c r="K2">
-        <v>56.5</v>
+        <v>56.6</v>
       </c>
       <c r="L2" t="s">
         <v>26</v>
@@ -549,7 +549,7 @@
         <v>27</v>
       </c>
       <c r="N2">
-        <v>50.43822221555986</v>
+        <v>50.56766494832259</v>
       </c>
       <c r="O2" t="s">
         <v>28</v>
@@ -587,7 +587,7 @@
         <v>53</v>
       </c>
       <c r="K3">
-        <v>54.3</v>
+        <v>54.4</v>
       </c>
       <c r="L3" t="s">
         <v>26</v>
@@ -596,7 +596,7 @@
         <v>27</v>
       </c>
       <c r="N3">
-        <v>50.43822221555986</v>
+        <v>50.56766494832259</v>
       </c>
       <c r="O3" t="s">
         <v>28</v>
@@ -634,7 +634,7 @@
         <v>73</v>
       </c>
       <c r="K4">
-        <v>51.3</v>
+        <v>51.4</v>
       </c>
       <c r="L4" t="s">
         <v>26</v>
@@ -643,7 +643,7 @@
         <v>27</v>
       </c>
       <c r="N4">
-        <v>50.43822221555986</v>
+        <v>50.56766494832259</v>
       </c>
       <c r="O4" t="s">
         <v>28</v>
@@ -681,7 +681,7 @@
         <v>80</v>
       </c>
       <c r="K5">
-        <v>50.3</v>
+        <v>50.4</v>
       </c>
       <c r="L5" t="s">
         <v>26</v>
@@ -690,7 +690,7 @@
         <v>27</v>
       </c>
       <c r="N5">
-        <v>50.43822221555986</v>
+        <v>50.56766494832259</v>
       </c>
       <c r="O5" t="s">
         <v>28</v>
@@ -728,7 +728,7 @@
         <v>63</v>
       </c>
       <c r="K6">
-        <v>49.5</v>
+        <v>49.6</v>
       </c>
       <c r="L6" t="s">
         <v>26</v>
@@ -737,7 +737,7 @@
         <v>27</v>
       </c>
       <c r="N6">
-        <v>50.43822221555986</v>
+        <v>50.56766494832259</v>
       </c>
       <c r="O6" t="s">
         <v>28</v>

--- a/DECISION/미장_반도체_분석.xlsx
+++ b/DECISION/미장_반도체_분석.xlsx
@@ -61,37 +61,37 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-01-12</t>
+    <t>2026-01-13</t>
   </si>
   <si>
     <t>Taiwan Semiconductor Manufactur</t>
   </si>
   <si>
+    <t>NVIDIA Corporation</t>
+  </si>
+  <si>
+    <t>ASML Holding N.V. - New York Re</t>
+  </si>
+  <si>
+    <t>Advanced Micro Devices, Inc.</t>
+  </si>
+  <si>
     <t>QUALCOMM Incorporated</t>
   </si>
   <si>
-    <t>NVIDIA Corporation</t>
-  </si>
-  <si>
-    <t>Advanced Micro Devices, Inc.</t>
-  </si>
-  <si>
-    <t>ASML Holding N.V. - New York Re</t>
-  </si>
-  <si>
     <t>TSM</t>
   </si>
   <si>
+    <t>NVDA</t>
+  </si>
+  <si>
+    <t>ASML</t>
+  </si>
+  <si>
+    <t>AMD</t>
+  </si>
+  <si>
     <t>QCOM</t>
-  </si>
-  <si>
-    <t>NVDA</t>
-  </si>
-  <si>
-    <t>AMD</t>
-  </si>
-  <si>
-    <t>ASML</t>
   </si>
   <si>
     <t>Pattern</t>
@@ -519,28 +519,28 @@
         <v>21</v>
       </c>
       <c r="D2">
-        <v>323.63</v>
+        <v>331.77</v>
       </c>
       <c r="E2">
-        <v>80.3</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="F2">
-        <v>1.26</v>
+        <v>2.95</v>
       </c>
       <c r="G2">
         <v>50</v>
       </c>
       <c r="H2">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="I2">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="J2">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="K2">
-        <v>56.6</v>
+        <v>58.6</v>
       </c>
       <c r="L2" t="s">
         <v>26</v>
@@ -549,7 +549,7 @@
         <v>27</v>
       </c>
       <c r="N2">
-        <v>50.56766494832259</v>
+        <v>47.98314273412904</v>
       </c>
       <c r="O2" t="s">
         <v>28</v>
@@ -566,28 +566,28 @@
         <v>22</v>
       </c>
       <c r="D3">
-        <v>177.78</v>
+        <v>184.94</v>
       </c>
       <c r="E3">
-        <v>56.8</v>
+        <v>57.9</v>
       </c>
       <c r="F3">
-        <v>2.77</v>
+        <v>-1.69</v>
       </c>
       <c r="G3">
+        <v>50</v>
+      </c>
+      <c r="H3">
         <v>60</v>
       </c>
-      <c r="H3">
-        <v>56</v>
-      </c>
       <c r="I3">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="J3">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="K3">
-        <v>54.4</v>
+        <v>54.6</v>
       </c>
       <c r="L3" t="s">
         <v>26</v>
@@ -596,7 +596,7 @@
         <v>27</v>
       </c>
       <c r="N3">
-        <v>50.56766494832259</v>
+        <v>47.98314273412904</v>
       </c>
       <c r="O3" t="s">
         <v>28</v>
@@ -613,28 +613,28 @@
         <v>23</v>
       </c>
       <c r="D4">
-        <v>184.86</v>
+        <v>1281.23</v>
       </c>
       <c r="E4">
-        <v>66.90000000000001</v>
+        <v>83.2</v>
       </c>
       <c r="F4">
-        <v>-2.11</v>
+        <v>4.32</v>
       </c>
       <c r="G4">
         <v>50</v>
       </c>
       <c r="H4">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="I4">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="J4">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="K4">
-        <v>51.4</v>
+        <v>54.6</v>
       </c>
       <c r="L4" t="s">
         <v>26</v>
@@ -643,7 +643,7 @@
         <v>27</v>
       </c>
       <c r="N4">
-        <v>50.56766494832259</v>
+        <v>47.98314273412904</v>
       </c>
       <c r="O4" t="s">
         <v>28</v>
@@ -660,19 +660,19 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>203.17</v>
+        <v>207.69</v>
       </c>
       <c r="E5">
-        <v>52.3</v>
+        <v>42.4</v>
       </c>
       <c r="F5">
-        <v>-9.08</v>
+        <v>-6.06</v>
       </c>
       <c r="G5">
         <v>20</v>
       </c>
       <c r="H5">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="I5">
         <v>73</v>
@@ -681,7 +681,7 @@
         <v>80</v>
       </c>
       <c r="K5">
-        <v>50.4</v>
+        <v>49.6</v>
       </c>
       <c r="L5" t="s">
         <v>26</v>
@@ -690,7 +690,7 @@
         <v>27</v>
       </c>
       <c r="N5">
-        <v>50.56766494832259</v>
+        <v>47.98314273412904</v>
       </c>
       <c r="O5" t="s">
         <v>28</v>
@@ -707,28 +707,28 @@
         <v>25</v>
       </c>
       <c r="D6">
-        <v>1273.88</v>
+        <v>169.27</v>
       </c>
       <c r="E6">
-        <v>83.8</v>
+        <v>41.1</v>
       </c>
       <c r="F6">
-        <v>9.460000000000001</v>
+        <v>-3.99</v>
       </c>
       <c r="G6">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H6">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="I6">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="J6">
         <v>63</v>
       </c>
       <c r="K6">
-        <v>49.6</v>
+        <v>43.4</v>
       </c>
       <c r="L6" t="s">
         <v>26</v>
@@ -737,7 +737,7 @@
         <v>27</v>
       </c>
       <c r="N6">
-        <v>50.56766494832259</v>
+        <v>47.98314273412904</v>
       </c>
       <c r="O6" t="s">
         <v>28</v>

--- a/DECISION/미장_반도체_분석.xlsx
+++ b/DECISION/미장_반도체_분석.xlsx
@@ -61,34 +61,34 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-01-13</t>
+    <t>2026-01-14</t>
+  </si>
+  <si>
+    <t>Advanced Micro Devices, Inc.</t>
+  </si>
+  <si>
+    <t>NVIDIA Corporation</t>
+  </si>
+  <si>
+    <t>ASML Holding N.V. - New York Re</t>
   </si>
   <si>
     <t>Taiwan Semiconductor Manufactur</t>
   </si>
   <si>
-    <t>NVIDIA Corporation</t>
-  </si>
-  <si>
-    <t>ASML Holding N.V. - New York Re</t>
-  </si>
-  <si>
-    <t>Advanced Micro Devices, Inc.</t>
-  </si>
-  <si>
     <t>QUALCOMM Incorporated</t>
   </si>
   <si>
+    <t>AMD</t>
+  </si>
+  <si>
+    <t>NVDA</t>
+  </si>
+  <si>
+    <t>ASML</t>
+  </si>
+  <si>
     <t>TSM</t>
-  </si>
-  <si>
-    <t>NVDA</t>
-  </si>
-  <si>
-    <t>ASML</t>
-  </si>
-  <si>
-    <t>AMD</t>
   </si>
   <si>
     <t>QCOM</t>
@@ -519,28 +519,28 @@
         <v>21</v>
       </c>
       <c r="D2">
-        <v>331.77</v>
+        <v>220.97</v>
       </c>
       <c r="E2">
-        <v>81.40000000000001</v>
+        <v>56.1</v>
       </c>
       <c r="F2">
-        <v>2.95</v>
+        <v>3.09</v>
       </c>
       <c r="G2">
         <v>50</v>
       </c>
       <c r="H2">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="I2">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="J2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K2">
-        <v>58.6</v>
+        <v>55.9</v>
       </c>
       <c r="L2" t="s">
         <v>26</v>
@@ -549,7 +549,7 @@
         <v>27</v>
       </c>
       <c r="N2">
-        <v>47.98314273412904</v>
+        <v>43.1153238131143</v>
       </c>
       <c r="O2" t="s">
         <v>28</v>
@@ -566,28 +566,28 @@
         <v>22</v>
       </c>
       <c r="D3">
-        <v>184.94</v>
+        <v>185.81</v>
       </c>
       <c r="E3">
-        <v>57.9</v>
+        <v>54.6</v>
       </c>
       <c r="F3">
-        <v>-1.69</v>
+        <v>-0.76</v>
       </c>
       <c r="G3">
+        <v>40</v>
+      </c>
+      <c r="H3">
         <v>50</v>
       </c>
-      <c r="H3">
-        <v>60</v>
-      </c>
       <c r="I3">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="J3">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="K3">
-        <v>54.6</v>
+        <v>54.1</v>
       </c>
       <c r="L3" t="s">
         <v>26</v>
@@ -596,7 +596,7 @@
         <v>27</v>
       </c>
       <c r="N3">
-        <v>47.98314273412904</v>
+        <v>43.1153238131143</v>
       </c>
       <c r="O3" t="s">
         <v>28</v>
@@ -613,13 +613,13 @@
         <v>23</v>
       </c>
       <c r="D4">
-        <v>1281.23</v>
+        <v>1270.16</v>
       </c>
       <c r="E4">
-        <v>83.2</v>
+        <v>80.5</v>
       </c>
       <c r="F4">
-        <v>4.32</v>
+        <v>2.25</v>
       </c>
       <c r="G4">
         <v>50</v>
@@ -631,10 +631,10 @@
         <v>63</v>
       </c>
       <c r="J4">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="K4">
-        <v>54.6</v>
+        <v>53.1</v>
       </c>
       <c r="L4" t="s">
         <v>26</v>
@@ -643,7 +643,7 @@
         <v>27</v>
       </c>
       <c r="N4">
-        <v>47.98314273412904</v>
+        <v>43.1153238131143</v>
       </c>
       <c r="O4" t="s">
         <v>28</v>
@@ -660,28 +660,28 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>207.69</v>
+        <v>331.21</v>
       </c>
       <c r="E5">
-        <v>42.4</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="F5">
-        <v>-6.06</v>
+        <v>1.15</v>
       </c>
       <c r="G5">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H5">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="I5">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="J5">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="K5">
-        <v>49.6</v>
+        <v>49.1</v>
       </c>
       <c r="L5" t="s">
         <v>26</v>
@@ -690,7 +690,7 @@
         <v>27</v>
       </c>
       <c r="N5">
-        <v>47.98314273412904</v>
+        <v>43.1153238131143</v>
       </c>
       <c r="O5" t="s">
         <v>28</v>
@@ -707,28 +707,28 @@
         <v>25</v>
       </c>
       <c r="D6">
-        <v>169.27</v>
+        <v>165.29</v>
       </c>
       <c r="E6">
-        <v>41.1</v>
+        <v>37.8</v>
       </c>
       <c r="F6">
-        <v>-3.99</v>
+        <v>-9.41</v>
       </c>
       <c r="G6">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="I6">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="J6">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="K6">
-        <v>43.4</v>
+        <v>35.3</v>
       </c>
       <c r="L6" t="s">
         <v>26</v>
@@ -737,7 +737,7 @@
         <v>27</v>
       </c>
       <c r="N6">
-        <v>47.98314273412904</v>
+        <v>43.1153238131143</v>
       </c>
       <c r="O6" t="s">
         <v>28</v>

--- a/DECISION/미장_반도체_분석.xlsx
+++ b/DECISION/미장_반도체_분석.xlsx
@@ -61,7 +61,10 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-01-14</t>
+    <t>2026-01-17</t>
+  </si>
+  <si>
+    <t>Taiwan Semiconductor Manufactur</t>
   </si>
   <si>
     <t>Advanced Micro Devices, Inc.</t>
@@ -73,12 +76,12 @@
     <t>ASML Holding N.V. - New York Re</t>
   </si>
   <si>
-    <t>Taiwan Semiconductor Manufactur</t>
-  </si>
-  <si>
     <t>QUALCOMM Incorporated</t>
   </si>
   <si>
+    <t>TSM</t>
+  </si>
+  <si>
     <t>AMD</t>
   </si>
   <si>
@@ -86,9 +89,6 @@
   </si>
   <si>
     <t>ASML</t>
-  </si>
-  <si>
-    <t>TSM</t>
   </si>
   <si>
     <t>QCOM</t>
@@ -519,28 +519,28 @@
         <v>21</v>
       </c>
       <c r="D2">
-        <v>220.97</v>
+        <v>342.4</v>
       </c>
       <c r="E2">
-        <v>56.1</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="F2">
-        <v>3.09</v>
+        <v>5.8</v>
       </c>
       <c r="G2">
         <v>50</v>
       </c>
       <c r="H2">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="I2">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="J2">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="K2">
-        <v>55.9</v>
+        <v>57.5</v>
       </c>
       <c r="L2" t="s">
         <v>26</v>
@@ -549,7 +549,7 @@
         <v>27</v>
       </c>
       <c r="N2">
-        <v>43.1153238131143</v>
+        <v>40.49436870247035</v>
       </c>
       <c r="O2" t="s">
         <v>28</v>
@@ -566,28 +566,28 @@
         <v>22</v>
       </c>
       <c r="D3">
-        <v>185.81</v>
+        <v>231.83</v>
       </c>
       <c r="E3">
-        <v>54.6</v>
+        <v>64</v>
       </c>
       <c r="F3">
-        <v>-0.76</v>
+        <v>14.11</v>
       </c>
       <c r="G3">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="H3">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="I3">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="J3">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="K3">
-        <v>54.1</v>
+        <v>53.5</v>
       </c>
       <c r="L3" t="s">
         <v>26</v>
@@ -596,7 +596,7 @@
         <v>27</v>
       </c>
       <c r="N3">
-        <v>43.1153238131143</v>
+        <v>40.49436870247035</v>
       </c>
       <c r="O3" t="s">
         <v>28</v>
@@ -613,28 +613,28 @@
         <v>23</v>
       </c>
       <c r="D4">
-        <v>1270.16</v>
+        <v>186.23</v>
       </c>
       <c r="E4">
-        <v>80.5</v>
+        <v>40.4</v>
       </c>
       <c r="F4">
-        <v>2.25</v>
+        <v>0.74</v>
       </c>
       <c r="G4">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H4">
         <v>70</v>
       </c>
       <c r="I4">
+        <v>66</v>
+      </c>
+      <c r="J4">
         <v>63</v>
       </c>
-      <c r="J4">
-        <v>73</v>
-      </c>
       <c r="K4">
-        <v>53.1</v>
+        <v>50.5</v>
       </c>
       <c r="L4" t="s">
         <v>26</v>
@@ -643,7 +643,7 @@
         <v>27</v>
       </c>
       <c r="N4">
-        <v>43.1153238131143</v>
+        <v>40.49436870247035</v>
       </c>
       <c r="O4" t="s">
         <v>28</v>
@@ -660,28 +660,28 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>331.21</v>
+        <v>1358.57</v>
       </c>
       <c r="E5">
-        <v>79.40000000000001</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="F5">
-        <v>1.15</v>
+        <v>6.65</v>
       </c>
       <c r="G5">
         <v>50</v>
       </c>
       <c r="H5">
+        <v>53</v>
+      </c>
+      <c r="I5">
+        <v>46</v>
+      </c>
+      <c r="J5">
         <v>66</v>
       </c>
-      <c r="I5">
-        <v>53</v>
-      </c>
-      <c r="J5">
-        <v>76</v>
-      </c>
       <c r="K5">
-        <v>49.1</v>
+        <v>45.5</v>
       </c>
       <c r="L5" t="s">
         <v>26</v>
@@ -690,7 +690,7 @@
         <v>27</v>
       </c>
       <c r="N5">
-        <v>43.1153238131143</v>
+        <v>40.49436870247035</v>
       </c>
       <c r="O5" t="s">
         <v>28</v>
@@ -707,28 +707,28 @@
         <v>25</v>
       </c>
       <c r="D6">
-        <v>165.29</v>
+        <v>159.42</v>
       </c>
       <c r="E6">
-        <v>37.8</v>
+        <v>31.7</v>
       </c>
       <c r="F6">
-        <v>-9.41</v>
+        <v>-10.33</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="I6">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="J6">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="K6">
-        <v>35.3</v>
+        <v>36.1</v>
       </c>
       <c r="L6" t="s">
         <v>26</v>
@@ -737,7 +737,7 @@
         <v>27</v>
       </c>
       <c r="N6">
-        <v>43.1153238131143</v>
+        <v>40.49436870247035</v>
       </c>
       <c r="O6" t="s">
         <v>28</v>

--- a/DECISION/미장_반도체_분석.xlsx
+++ b/DECISION/미장_반도체_분석.xlsx
@@ -61,7 +61,7 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-01-17</t>
+    <t>2026-01-19</t>
   </si>
   <si>
     <t>Taiwan Semiconductor Manufactur</t>
@@ -549,7 +549,7 @@
         <v>27</v>
       </c>
       <c r="N2">
-        <v>40.49436870247035</v>
+        <v>40.44495449250464</v>
       </c>
       <c r="O2" t="s">
         <v>28</v>
@@ -596,7 +596,7 @@
         <v>27</v>
       </c>
       <c r="N3">
-        <v>40.49436870247035</v>
+        <v>40.44495449250464</v>
       </c>
       <c r="O3" t="s">
         <v>28</v>
@@ -643,7 +643,7 @@
         <v>27</v>
       </c>
       <c r="N4">
-        <v>40.49436870247035</v>
+        <v>40.44495449250464</v>
       </c>
       <c r="O4" t="s">
         <v>28</v>
@@ -690,7 +690,7 @@
         <v>27</v>
       </c>
       <c r="N5">
-        <v>40.49436870247035</v>
+        <v>40.44495449250464</v>
       </c>
       <c r="O5" t="s">
         <v>28</v>
@@ -737,7 +737,7 @@
         <v>27</v>
       </c>
       <c r="N6">
-        <v>40.49436870247035</v>
+        <v>40.44495449250464</v>
       </c>
       <c r="O6" t="s">
         <v>28</v>

--- a/DECISION/미장_반도체_분석.xlsx
+++ b/DECISION/미장_반도체_분석.xlsx
@@ -61,46 +61,46 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-01-19</t>
+    <t>2026-03-03</t>
+  </si>
+  <si>
+    <t>NVIDIA Corporation</t>
+  </si>
+  <si>
+    <t>QUALCOMM Incorporated</t>
   </si>
   <si>
     <t>Taiwan Semiconductor Manufactur</t>
   </si>
   <si>
+    <t>ASML Holding N.V. - New York Re</t>
+  </si>
+  <si>
     <t>Advanced Micro Devices, Inc.</t>
   </si>
   <si>
-    <t>NVIDIA Corporation</t>
-  </si>
-  <si>
-    <t>ASML Holding N.V. - New York Re</t>
-  </si>
-  <si>
-    <t>QUALCOMM Incorporated</t>
+    <t>NVDA</t>
+  </si>
+  <si>
+    <t>QCOM</t>
   </si>
   <si>
     <t>TSM</t>
   </si>
   <si>
+    <t>ASML</t>
+  </si>
+  <si>
     <t>AMD</t>
   </si>
   <si>
-    <t>NVDA</t>
-  </si>
-  <si>
-    <t>ASML</t>
-  </si>
-  <si>
-    <t>QCOM</t>
-  </si>
-  <si>
     <t>Pattern</t>
   </si>
   <si>
     <t>⛔ 관망하십시오.</t>
   </si>
   <si>
-    <t>⚪ 중립 구간</t>
+    <t>🔴 강한 긴축 / 리스크</t>
   </si>
 </sst>
 </file>
@@ -519,28 +519,28 @@
         <v>21</v>
       </c>
       <c r="D2">
-        <v>342.4</v>
+        <v>182.48</v>
       </c>
       <c r="E2">
-        <v>76.59999999999999</v>
+        <v>41.9</v>
       </c>
       <c r="F2">
-        <v>5.8</v>
+        <v>-4.74</v>
       </c>
       <c r="G2">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H2">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="I2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="J2">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="K2">
-        <v>57.5</v>
+        <v>47.1</v>
       </c>
       <c r="L2" t="s">
         <v>26</v>
@@ -549,7 +549,7 @@
         <v>27</v>
       </c>
       <c r="N2">
-        <v>40.44495449250464</v>
+        <v>20.49503599836755</v>
       </c>
       <c r="O2" t="s">
         <v>28</v>
@@ -566,28 +566,28 @@
         <v>22</v>
       </c>
       <c r="D3">
-        <v>231.83</v>
+        <v>141.03</v>
       </c>
       <c r="E3">
-        <v>64</v>
+        <v>54.1</v>
       </c>
       <c r="F3">
-        <v>14.11</v>
+        <v>0.44</v>
       </c>
       <c r="G3">
         <v>50</v>
       </c>
       <c r="H3">
+        <v>50</v>
+      </c>
+      <c r="I3">
         <v>63</v>
       </c>
-      <c r="I3">
+      <c r="J3">
         <v>66</v>
       </c>
-      <c r="J3">
-        <v>80</v>
-      </c>
       <c r="K3">
-        <v>53.5</v>
+        <v>46.3</v>
       </c>
       <c r="L3" t="s">
         <v>26</v>
@@ -596,7 +596,7 @@
         <v>27</v>
       </c>
       <c r="N3">
-        <v>40.44495449250464</v>
+        <v>20.49503599836755</v>
       </c>
       <c r="O3" t="s">
         <v>28</v>
@@ -613,28 +613,28 @@
         <v>23</v>
       </c>
       <c r="D4">
-        <v>186.23</v>
+        <v>369.11</v>
       </c>
       <c r="E4">
-        <v>40.4</v>
+        <v>58.6</v>
       </c>
       <c r="F4">
-        <v>0.74</v>
+        <v>-0.25</v>
       </c>
       <c r="G4">
         <v>40</v>
       </c>
       <c r="H4">
+        <v>63</v>
+      </c>
+      <c r="I4">
         <v>70</v>
       </c>
-      <c r="I4">
-        <v>66</v>
-      </c>
       <c r="J4">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="K4">
-        <v>50.5</v>
+        <v>46.1</v>
       </c>
       <c r="L4" t="s">
         <v>26</v>
@@ -643,7 +643,7 @@
         <v>27</v>
       </c>
       <c r="N4">
-        <v>40.44495449250464</v>
+        <v>20.49503599836755</v>
       </c>
       <c r="O4" t="s">
         <v>28</v>
@@ -660,28 +660,28 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>1358.57</v>
+        <v>1423.54</v>
       </c>
       <c r="E5">
-        <v>82.90000000000001</v>
+        <v>49.3</v>
       </c>
       <c r="F5">
-        <v>6.65</v>
+        <v>-4.2</v>
       </c>
       <c r="G5">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H5">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="I5">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="J5">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="K5">
-        <v>45.5</v>
+        <v>40.3</v>
       </c>
       <c r="L5" t="s">
         <v>26</v>
@@ -690,7 +690,7 @@
         <v>27</v>
       </c>
       <c r="N5">
-        <v>40.44495449250464</v>
+        <v>20.49503599836755</v>
       </c>
       <c r="O5" t="s">
         <v>28</v>
@@ -707,28 +707,28 @@
         <v>25</v>
       </c>
       <c r="D6">
-        <v>159.42</v>
+        <v>198.62</v>
       </c>
       <c r="E6">
-        <v>31.7</v>
+        <v>35.8</v>
       </c>
       <c r="F6">
-        <v>-10.33</v>
+        <v>1.03</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H6">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="I6">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="J6">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="K6">
-        <v>36.1</v>
+        <v>40.1</v>
       </c>
       <c r="L6" t="s">
         <v>26</v>
@@ -737,7 +737,7 @@
         <v>27</v>
       </c>
       <c r="N6">
-        <v>40.44495449250464</v>
+        <v>20.49503599836755</v>
       </c>
       <c r="O6" t="s">
         <v>28</v>

--- a/DECISION/미장_반도체_분석.xlsx
+++ b/DECISION/미장_반도체_분석.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="30">
   <si>
     <t>날짜</t>
   </si>
@@ -61,7 +61,7 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-03-03</t>
+    <t>2026-03-09</t>
   </si>
   <si>
     <t>NVIDIA Corporation</t>
@@ -70,34 +70,37 @@
     <t>QUALCOMM Incorporated</t>
   </si>
   <si>
+    <t>Advanced Micro Devices, Inc.</t>
+  </si>
+  <si>
+    <t>ASML Holding N.V. - New York Re</t>
+  </si>
+  <si>
     <t>Taiwan Semiconductor Manufactur</t>
   </si>
   <si>
-    <t>ASML Holding N.V. - New York Re</t>
-  </si>
-  <si>
-    <t>Advanced Micro Devices, Inc.</t>
-  </si>
-  <si>
     <t>NVDA</t>
   </si>
   <si>
     <t>QCOM</t>
   </si>
   <si>
+    <t>AMD</t>
+  </si>
+  <si>
+    <t>ASML</t>
+  </si>
+  <si>
     <t>TSM</t>
   </si>
   <si>
-    <t>ASML</t>
-  </si>
-  <si>
-    <t>AMD</t>
-  </si>
-  <si>
     <t>Pattern</t>
   </si>
   <si>
     <t>⛔ 관망하십시오.</t>
+  </si>
+  <si>
+    <t>🤏 바닥권 접근 구간입니다.</t>
   </si>
   <si>
     <t>🔴 강한 긴축 / 리스크</t>
@@ -519,28 +522,28 @@
         <v>21</v>
       </c>
       <c r="D2">
-        <v>182.48</v>
+        <v>177.82</v>
       </c>
       <c r="E2">
-        <v>41.9</v>
+        <v>44.8</v>
       </c>
       <c r="F2">
-        <v>-4.74</v>
+        <v>0.36</v>
       </c>
       <c r="G2">
         <v>30</v>
       </c>
       <c r="H2">
+        <v>66</v>
+      </c>
+      <c r="I2">
+        <v>70</v>
+      </c>
+      <c r="J2">
         <v>60</v>
       </c>
-      <c r="I2">
-        <v>80</v>
-      </c>
-      <c r="J2">
-        <v>66</v>
-      </c>
       <c r="K2">
-        <v>47.1</v>
+        <v>38.3</v>
       </c>
       <c r="L2" t="s">
         <v>26</v>
@@ -549,10 +552,10 @@
         <v>27</v>
       </c>
       <c r="N2">
-        <v>20.49503599836755</v>
+        <v>4.469434098808478</v>
       </c>
       <c r="O2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -566,28 +569,28 @@
         <v>22</v>
       </c>
       <c r="D3">
-        <v>141.03</v>
+        <v>135.69</v>
       </c>
       <c r="E3">
-        <v>54.1</v>
+        <v>42</v>
       </c>
       <c r="F3">
-        <v>0.44</v>
+        <v>-4.07</v>
       </c>
       <c r="G3">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H3">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="I3">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="J3">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="K3">
-        <v>46.3</v>
+        <v>36.7</v>
       </c>
       <c r="L3" t="s">
         <v>26</v>
@@ -596,10 +599,10 @@
         <v>27</v>
       </c>
       <c r="N3">
-        <v>20.49503599836755</v>
+        <v>4.469434098808478</v>
       </c>
       <c r="O3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -613,28 +616,28 @@
         <v>23</v>
       </c>
       <c r="D4">
-        <v>369.11</v>
+        <v>192.43</v>
       </c>
       <c r="E4">
-        <v>58.6</v>
+        <v>40.5</v>
       </c>
       <c r="F4">
-        <v>-0.25</v>
+        <v>-3.89</v>
       </c>
       <c r="G4">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="H4">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="I4">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="J4">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="K4">
-        <v>46.1</v>
+        <v>36.5</v>
       </c>
       <c r="L4" t="s">
         <v>26</v>
@@ -643,10 +646,10 @@
         <v>27</v>
       </c>
       <c r="N4">
-        <v>20.49503599836755</v>
+        <v>4.469434098808478</v>
       </c>
       <c r="O4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -660,40 +663,40 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>1423.54</v>
+        <v>1292.8</v>
       </c>
       <c r="E5">
-        <v>49.3</v>
+        <v>37.4</v>
       </c>
       <c r="F5">
-        <v>-4.2</v>
+        <v>-10.88</v>
       </c>
       <c r="G5">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="I5">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="J5">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="K5">
-        <v>40.3</v>
+        <v>25.3</v>
       </c>
       <c r="L5" t="s">
         <v>26</v>
       </c>
       <c r="M5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="N5">
-        <v>20.49503599836755</v>
+        <v>4.469434098808478</v>
       </c>
       <c r="O5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:15">
@@ -707,28 +710,28 @@
         <v>25</v>
       </c>
       <c r="D6">
-        <v>198.62</v>
+        <v>338.89</v>
       </c>
       <c r="E6">
-        <v>35.8</v>
+        <v>35</v>
       </c>
       <c r="F6">
-        <v>1.03</v>
+        <v>-9.529999999999999</v>
       </c>
       <c r="G6">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="I6">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="J6">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="K6">
-        <v>40.1</v>
+        <v>22.5</v>
       </c>
       <c r="L6" t="s">
         <v>26</v>
@@ -737,10 +740,10 @@
         <v>27</v>
       </c>
       <c r="N6">
-        <v>20.49503599836755</v>
+        <v>4.469434098808478</v>
       </c>
       <c r="O6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/DECISION/미장_반도체_분석.xlsx
+++ b/DECISION/미장_반도체_분석.xlsx
@@ -543,7 +543,7 @@
         <v>60</v>
       </c>
       <c r="K2">
-        <v>38.3</v>
+        <v>37</v>
       </c>
       <c r="L2" t="s">
         <v>26</v>
@@ -552,7 +552,7 @@
         <v>27</v>
       </c>
       <c r="N2">
-        <v>4.469434098808478</v>
+        <v>0</v>
       </c>
       <c r="O2" t="s">
         <v>29</v>
@@ -590,7 +590,7 @@
         <v>56</v>
       </c>
       <c r="K3">
-        <v>36.7</v>
+        <v>35.4</v>
       </c>
       <c r="L3" t="s">
         <v>26</v>
@@ -599,7 +599,7 @@
         <v>27</v>
       </c>
       <c r="N3">
-        <v>4.469434098808478</v>
+        <v>0</v>
       </c>
       <c r="O3" t="s">
         <v>29</v>
@@ -637,7 +637,7 @@
         <v>66</v>
       </c>
       <c r="K4">
-        <v>36.5</v>
+        <v>35.2</v>
       </c>
       <c r="L4" t="s">
         <v>26</v>
@@ -646,7 +646,7 @@
         <v>27</v>
       </c>
       <c r="N4">
-        <v>4.469434098808478</v>
+        <v>0</v>
       </c>
       <c r="O4" t="s">
         <v>29</v>
@@ -684,7 +684,7 @@
         <v>70</v>
       </c>
       <c r="K5">
-        <v>25.3</v>
+        <v>24</v>
       </c>
       <c r="L5" t="s">
         <v>26</v>
@@ -693,7 +693,7 @@
         <v>28</v>
       </c>
       <c r="N5">
-        <v>4.469434098808478</v>
+        <v>0</v>
       </c>
       <c r="O5" t="s">
         <v>29</v>
@@ -731,7 +731,7 @@
         <v>66</v>
       </c>
       <c r="K6">
-        <v>22.5</v>
+        <v>21.2</v>
       </c>
       <c r="L6" t="s">
         <v>26</v>
@@ -740,7 +740,7 @@
         <v>27</v>
       </c>
       <c r="N6">
-        <v>4.469434098808478</v>
+        <v>0</v>
       </c>
       <c r="O6" t="s">
         <v>29</v>

--- a/DECISION/미장_반도체_분석.xlsx
+++ b/DECISION/미장_반도체_분석.xlsx
@@ -61,39 +61,39 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-03-09</t>
+    <t>2026-03-10</t>
+  </si>
+  <si>
+    <t>Advanced Micro Devices, Inc.</t>
   </si>
   <si>
     <t>NVIDIA Corporation</t>
   </si>
   <si>
+    <t>Taiwan Semiconductor Manufactur</t>
+  </si>
+  <si>
     <t>QUALCOMM Incorporated</t>
   </si>
   <si>
-    <t>Advanced Micro Devices, Inc.</t>
-  </si>
-  <si>
     <t>ASML Holding N.V. - New York Re</t>
   </si>
   <si>
-    <t>Taiwan Semiconductor Manufactur</t>
+    <t>AMD</t>
   </si>
   <si>
     <t>NVDA</t>
   </si>
   <si>
+    <t>TSM</t>
+  </si>
+  <si>
     <t>QCOM</t>
   </si>
   <si>
-    <t>AMD</t>
-  </si>
-  <si>
     <t>ASML</t>
   </si>
   <si>
-    <t>TSM</t>
-  </si>
-  <si>
     <t>Pattern</t>
   </si>
   <si>
@@ -103,7 +103,7 @@
     <t>🤏 바닥권 접근 구간입니다.</t>
   </si>
   <si>
-    <t>🔴 강한 긴축 / 리스크</t>
+    <t>🟠 하락 우위 (긴장 구간)</t>
   </si>
 </sst>
 </file>
@@ -522,28 +522,28 @@
         <v>21</v>
       </c>
       <c r="D2">
-        <v>177.82</v>
+        <v>202.68</v>
       </c>
       <c r="E2">
-        <v>44.8</v>
+        <v>49.8</v>
       </c>
       <c r="F2">
-        <v>0.36</v>
+        <v>2.04</v>
       </c>
       <c r="G2">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H2">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="I2">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="J2">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="K2">
-        <v>37</v>
+        <v>52.1</v>
       </c>
       <c r="L2" t="s">
         <v>26</v>
@@ -552,7 +552,7 @@
         <v>27</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>32.23518188264562</v>
       </c>
       <c r="O2" t="s">
         <v>29</v>
@@ -569,28 +569,28 @@
         <v>22</v>
       </c>
       <c r="D3">
-        <v>135.69</v>
+        <v>182.65</v>
       </c>
       <c r="E3">
-        <v>42</v>
+        <v>47.7</v>
       </c>
       <c r="F3">
-        <v>-4.07</v>
+        <v>0.09</v>
       </c>
       <c r="G3">
         <v>30</v>
       </c>
       <c r="H3">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="I3">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="J3">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="K3">
-        <v>35.4</v>
+        <v>42.7</v>
       </c>
       <c r="L3" t="s">
         <v>26</v>
@@ -599,7 +599,7 @@
         <v>27</v>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>32.23518188264562</v>
       </c>
       <c r="O3" t="s">
         <v>29</v>
@@ -616,28 +616,28 @@
         <v>23</v>
       </c>
       <c r="D4">
-        <v>192.43</v>
+        <v>348.7</v>
       </c>
       <c r="E4">
-        <v>40.5</v>
+        <v>42.2</v>
       </c>
       <c r="F4">
-        <v>-3.89</v>
+        <v>-5.53</v>
       </c>
       <c r="G4">
         <v>20</v>
       </c>
       <c r="H4">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="I4">
+        <v>63</v>
+      </c>
+      <c r="J4">
         <v>73</v>
       </c>
-      <c r="J4">
-        <v>66</v>
-      </c>
       <c r="K4">
-        <v>35.2</v>
+        <v>40.9</v>
       </c>
       <c r="L4" t="s">
         <v>26</v>
@@ -646,7 +646,7 @@
         <v>27</v>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>32.23518188264562</v>
       </c>
       <c r="O4" t="s">
         <v>29</v>
@@ -663,37 +663,37 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>1292.8</v>
+        <v>138.11</v>
       </c>
       <c r="E5">
-        <v>37.4</v>
+        <v>43.2</v>
       </c>
       <c r="F5">
-        <v>-10.88</v>
+        <v>-1.44</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H5">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="I5">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="J5">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="K5">
-        <v>24</v>
+        <v>38.7</v>
       </c>
       <c r="L5" t="s">
         <v>26</v>
       </c>
       <c r="M5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>32.23518188264562</v>
       </c>
       <c r="O5" t="s">
         <v>29</v>
@@ -710,37 +710,37 @@
         <v>25</v>
       </c>
       <c r="D6">
-        <v>338.89</v>
+        <v>1357.42</v>
       </c>
       <c r="E6">
-        <v>35</v>
+        <v>43.8</v>
       </c>
       <c r="F6">
-        <v>-9.529999999999999</v>
+        <v>-4.64</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H6">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="I6">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="J6">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="K6">
-        <v>21.2</v>
+        <v>32.9</v>
       </c>
       <c r="L6" t="s">
         <v>26</v>
       </c>
       <c r="M6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>32.23518188264562</v>
       </c>
       <c r="O6" t="s">
         <v>29</v>

--- a/DECISION/미장_반도체_분석.xlsx
+++ b/DECISION/미장_반도체_분석.xlsx
@@ -552,7 +552,7 @@
         <v>27</v>
       </c>
       <c r="N2">
-        <v>32.23518188264562</v>
+        <v>32.42054265786911</v>
       </c>
       <c r="O2" t="s">
         <v>29</v>
@@ -599,7 +599,7 @@
         <v>27</v>
       </c>
       <c r="N3">
-        <v>32.23518188264562</v>
+        <v>32.42054265786911</v>
       </c>
       <c r="O3" t="s">
         <v>29</v>
@@ -646,7 +646,7 @@
         <v>27</v>
       </c>
       <c r="N4">
-        <v>32.23518188264562</v>
+        <v>32.42054265786911</v>
       </c>
       <c r="O4" t="s">
         <v>29</v>
@@ -693,7 +693,7 @@
         <v>27</v>
       </c>
       <c r="N5">
-        <v>32.23518188264562</v>
+        <v>32.42054265786911</v>
       </c>
       <c r="O5" t="s">
         <v>29</v>
@@ -740,7 +740,7 @@
         <v>28</v>
       </c>
       <c r="N6">
-        <v>32.23518188264562</v>
+        <v>32.42054265786911</v>
       </c>
       <c r="O6" t="s">
         <v>29</v>

--- a/DECISION/미장_반도체_분석.xlsx
+++ b/DECISION/미장_반도체_분석.xlsx
@@ -61,7 +61,7 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-03-10</t>
+    <t>2026-03-11</t>
   </si>
   <si>
     <t>Advanced Micro Devices, Inc.</t>
@@ -73,12 +73,12 @@
     <t>Taiwan Semiconductor Manufactur</t>
   </si>
   <si>
+    <t>ASML Holding N.V. - New York Re</t>
+  </si>
+  <si>
     <t>QUALCOMM Incorporated</t>
   </si>
   <si>
-    <t>ASML Holding N.V. - New York Re</t>
-  </si>
-  <si>
     <t>AMD</t>
   </si>
   <si>
@@ -88,22 +88,22 @@
     <t>TSM</t>
   </si>
   <si>
+    <t>ASML</t>
+  </si>
+  <si>
     <t>QCOM</t>
   </si>
   <si>
-    <t>ASML</t>
-  </si>
-  <si>
     <t>Pattern</t>
   </si>
   <si>
+    <t>📈 매수 관찰 구간입니다.</t>
+  </si>
+  <si>
     <t>⛔ 관망하십시오.</t>
   </si>
   <si>
-    <t>🤏 바닥권 접근 구간입니다.</t>
-  </si>
-  <si>
-    <t>🟠 하락 우위 (긴장 구간)</t>
+    <t>⚪ 중립 구간</t>
   </si>
 </sst>
 </file>
@@ -522,28 +522,28 @@
         <v>21</v>
       </c>
       <c r="D2">
-        <v>202.68</v>
+        <v>203.23</v>
       </c>
       <c r="E2">
-        <v>49.8</v>
+        <v>51.9</v>
       </c>
       <c r="F2">
-        <v>2.04</v>
+        <v>6.43</v>
       </c>
       <c r="G2">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="H2">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="I2">
+        <v>80</v>
+      </c>
+      <c r="J2">
         <v>76</v>
       </c>
-      <c r="J2">
-        <v>73</v>
-      </c>
       <c r="K2">
-        <v>52.1</v>
+        <v>60</v>
       </c>
       <c r="L2" t="s">
         <v>26</v>
@@ -552,7 +552,7 @@
         <v>27</v>
       </c>
       <c r="N2">
-        <v>32.42054265786911</v>
+        <v>43.44936356612781</v>
       </c>
       <c r="O2" t="s">
         <v>29</v>
@@ -569,37 +569,37 @@
         <v>22</v>
       </c>
       <c r="D3">
-        <v>182.65</v>
+        <v>184.77</v>
       </c>
       <c r="E3">
-        <v>47.7</v>
+        <v>46.8</v>
       </c>
       <c r="F3">
-        <v>0.09</v>
+        <v>2.62</v>
       </c>
       <c r="G3">
         <v>30</v>
       </c>
       <c r="H3">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="I3">
         <v>60</v>
       </c>
       <c r="J3">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="K3">
-        <v>42.7</v>
+        <v>46</v>
       </c>
       <c r="L3" t="s">
         <v>26</v>
       </c>
       <c r="M3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="N3">
-        <v>32.42054265786911</v>
+        <v>43.44936356612781</v>
       </c>
       <c r="O3" t="s">
         <v>29</v>
@@ -616,13 +616,13 @@
         <v>23</v>
       </c>
       <c r="D4">
-        <v>348.7</v>
+        <v>347.09</v>
       </c>
       <c r="E4">
-        <v>42.2</v>
+        <v>42.3</v>
       </c>
       <c r="F4">
-        <v>-5.53</v>
+        <v>-1.71</v>
       </c>
       <c r="G4">
         <v>20</v>
@@ -631,22 +631,22 @@
         <v>53</v>
       </c>
       <c r="I4">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="J4">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="K4">
-        <v>40.9</v>
+        <v>43</v>
       </c>
       <c r="L4" t="s">
         <v>26</v>
       </c>
       <c r="M4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="N4">
-        <v>32.42054265786911</v>
+        <v>43.44936356612781</v>
       </c>
       <c r="O4" t="s">
         <v>29</v>
@@ -663,37 +663,37 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>138.11</v>
+        <v>1383.4</v>
       </c>
       <c r="E5">
-        <v>43.2</v>
+        <v>41.1</v>
       </c>
       <c r="F5">
-        <v>-1.44</v>
+        <v>1.65</v>
       </c>
       <c r="G5">
         <v>30</v>
       </c>
       <c r="H5">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="I5">
         <v>50</v>
       </c>
       <c r="J5">
-        <v>46</v>
+        <v>76</v>
       </c>
       <c r="K5">
-        <v>38.7</v>
+        <v>42</v>
       </c>
       <c r="L5" t="s">
         <v>26</v>
       </c>
       <c r="M5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="N5">
-        <v>32.42054265786911</v>
+        <v>43.44936356612781</v>
       </c>
       <c r="O5" t="s">
         <v>29</v>
@@ -710,28 +710,28 @@
         <v>25</v>
       </c>
       <c r="D6">
-        <v>1357.42</v>
+        <v>135.2</v>
       </c>
       <c r="E6">
-        <v>43.8</v>
+        <v>37.6</v>
       </c>
       <c r="F6">
-        <v>-4.64</v>
+        <v>-1.49</v>
       </c>
       <c r="G6">
         <v>20</v>
       </c>
       <c r="H6">
+        <v>63</v>
+      </c>
+      <c r="I6">
+        <v>56</v>
+      </c>
+      <c r="J6">
         <v>50</v>
       </c>
-      <c r="I6">
-        <v>43</v>
-      </c>
-      <c r="J6">
-        <v>73</v>
-      </c>
       <c r="K6">
-        <v>32.9</v>
+        <v>41.4</v>
       </c>
       <c r="L6" t="s">
         <v>26</v>
@@ -740,7 +740,7 @@
         <v>28</v>
       </c>
       <c r="N6">
-        <v>32.42054265786911</v>
+        <v>43.44936356612781</v>
       </c>
       <c r="O6" t="s">
         <v>29</v>

--- a/DECISION/미장_반도체_분석.xlsx
+++ b/DECISION/미장_반도체_분석.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="29">
   <si>
     <t>날짜</t>
   </si>
@@ -61,7 +61,7 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-03-11</t>
+    <t>2026-03-12</t>
   </si>
   <si>
     <t>Advanced Micro Devices, Inc.</t>
@@ -73,12 +73,12 @@
     <t>Taiwan Semiconductor Manufactur</t>
   </si>
   <si>
+    <t>QUALCOMM Incorporated</t>
+  </si>
+  <si>
     <t>ASML Holding N.V. - New York Re</t>
   </si>
   <si>
-    <t>QUALCOMM Incorporated</t>
-  </si>
-  <si>
     <t>AMD</t>
   </si>
   <si>
@@ -88,16 +88,13 @@
     <t>TSM</t>
   </si>
   <si>
+    <t>QCOM</t>
+  </si>
+  <si>
     <t>ASML</t>
   </si>
   <si>
-    <t>QCOM</t>
-  </si>
-  <si>
     <t>Pattern</t>
-  </si>
-  <si>
-    <t>📈 매수 관찰 구간입니다.</t>
   </si>
   <si>
     <t>⛔ 관망하십시오.</t>
@@ -522,28 +519,28 @@
         <v>21</v>
       </c>
       <c r="D2">
-        <v>203.23</v>
+        <v>204.83</v>
       </c>
       <c r="E2">
-        <v>51.9</v>
+        <v>50.9</v>
       </c>
       <c r="F2">
-        <v>6.43</v>
+        <v>1.37</v>
       </c>
       <c r="G2">
         <v>50</v>
       </c>
       <c r="H2">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="I2">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="J2">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="K2">
-        <v>60</v>
+        <v>52.7</v>
       </c>
       <c r="L2" t="s">
         <v>26</v>
@@ -552,10 +549,10 @@
         <v>27</v>
       </c>
       <c r="N2">
-        <v>43.44936356612781</v>
+        <v>41.74287521812095</v>
       </c>
       <c r="O2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -569,40 +566,40 @@
         <v>22</v>
       </c>
       <c r="D3">
-        <v>184.77</v>
+        <v>186.03</v>
       </c>
       <c r="E3">
-        <v>46.8</v>
+        <v>48.2</v>
       </c>
       <c r="F3">
-        <v>2.62</v>
+        <v>1.64</v>
       </c>
       <c r="G3">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H3">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="I3">
+        <v>56</v>
+      </c>
+      <c r="J3">
         <v>60</v>
       </c>
-      <c r="J3">
-        <v>73</v>
-      </c>
       <c r="K3">
-        <v>46</v>
+        <v>46.9</v>
       </c>
       <c r="L3" t="s">
         <v>26</v>
       </c>
       <c r="M3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N3">
+        <v>41.74287521812095</v>
+      </c>
+      <c r="O3" t="s">
         <v>28</v>
-      </c>
-      <c r="N3">
-        <v>43.44936356612781</v>
-      </c>
-      <c r="O3" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -616,40 +613,40 @@
         <v>23</v>
       </c>
       <c r="D4">
-        <v>347.09</v>
+        <v>354.56</v>
       </c>
       <c r="E4">
-        <v>42.3</v>
+        <v>47.2</v>
       </c>
       <c r="F4">
-        <v>-1.71</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="G4">
         <v>20</v>
       </c>
       <c r="H4">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="I4">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="J4">
         <v>76</v>
       </c>
       <c r="K4">
-        <v>43</v>
+        <v>43.7</v>
       </c>
       <c r="L4" t="s">
         <v>26</v>
       </c>
       <c r="M4" t="s">
+        <v>27</v>
+      </c>
+      <c r="N4">
+        <v>41.74287521812095</v>
+      </c>
+      <c r="O4" t="s">
         <v>28</v>
-      </c>
-      <c r="N4">
-        <v>43.44936356612781</v>
-      </c>
-      <c r="O4" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -663,40 +660,40 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>1383.4</v>
+        <v>134.12</v>
       </c>
       <c r="E5">
-        <v>41.1</v>
+        <v>38.8</v>
       </c>
       <c r="F5">
-        <v>1.65</v>
+        <v>-3.25</v>
       </c>
       <c r="G5">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H5">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="I5">
+        <v>56</v>
+      </c>
+      <c r="J5">
         <v>50</v>
       </c>
-      <c r="J5">
-        <v>76</v>
-      </c>
       <c r="K5">
-        <v>42</v>
+        <v>40.9</v>
       </c>
       <c r="L5" t="s">
         <v>26</v>
       </c>
       <c r="M5" t="s">
+        <v>27</v>
+      </c>
+      <c r="N5">
+        <v>41.74287521812095</v>
+      </c>
+      <c r="O5" t="s">
         <v>28</v>
-      </c>
-      <c r="N5">
-        <v>43.44936356612781</v>
-      </c>
-      <c r="O5" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:15">
@@ -710,40 +707,40 @@
         <v>25</v>
       </c>
       <c r="D6">
-        <v>135.2</v>
+        <v>1386.68</v>
       </c>
       <c r="E6">
-        <v>37.6</v>
+        <v>42.3</v>
       </c>
       <c r="F6">
-        <v>-1.49</v>
+        <v>-0.91</v>
       </c>
       <c r="G6">
         <v>20</v>
       </c>
       <c r="H6">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="I6">
         <v>56</v>
       </c>
       <c r="J6">
-        <v>50</v>
+        <v>83</v>
       </c>
       <c r="K6">
-        <v>41.4</v>
+        <v>40.9</v>
       </c>
       <c r="L6" t="s">
         <v>26</v>
       </c>
       <c r="M6" t="s">
+        <v>27</v>
+      </c>
+      <c r="N6">
+        <v>41.74287521812095</v>
+      </c>
+      <c r="O6" t="s">
         <v>28</v>
-      </c>
-      <c r="N6">
-        <v>43.44936356612781</v>
-      </c>
-      <c r="O6" t="s">
-        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/DECISION/미장_반도체_분석.xlsx
+++ b/DECISION/미장_반도체_분석.xlsx
@@ -549,7 +549,7 @@
         <v>27</v>
       </c>
       <c r="N2">
-        <v>41.74287521812095</v>
+        <v>41.81508460778518</v>
       </c>
       <c r="O2" t="s">
         <v>28</v>
@@ -596,7 +596,7 @@
         <v>27</v>
       </c>
       <c r="N3">
-        <v>41.74287521812095</v>
+        <v>41.81508460778518</v>
       </c>
       <c r="O3" t="s">
         <v>28</v>
@@ -643,7 +643,7 @@
         <v>27</v>
       </c>
       <c r="N4">
-        <v>41.74287521812095</v>
+        <v>41.81508460778518</v>
       </c>
       <c r="O4" t="s">
         <v>28</v>
@@ -690,7 +690,7 @@
         <v>27</v>
       </c>
       <c r="N5">
-        <v>41.74287521812095</v>
+        <v>41.81508460778518</v>
       </c>
       <c r="O5" t="s">
         <v>28</v>
@@ -737,7 +737,7 @@
         <v>27</v>
       </c>
       <c r="N6">
-        <v>41.74287521812095</v>
+        <v>41.81508460778518</v>
       </c>
       <c r="O6" t="s">
         <v>28</v>

--- a/DECISION/미장_반도체_분석.xlsx
+++ b/DECISION/미장_반도체_분석.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="30">
   <si>
     <t>날짜</t>
   </si>
@@ -61,7 +61,10 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-03-12</t>
+    <t>2026-04-08</t>
+  </si>
+  <si>
+    <t>Taiwan Semiconductor Manufactur</t>
   </si>
   <si>
     <t>Advanced Micro Devices, Inc.</t>
@@ -70,13 +73,13 @@
     <t>NVIDIA Corporation</t>
   </si>
   <si>
-    <t>Taiwan Semiconductor Manufactur</t>
+    <t>ASML Holding N.V. - New York Re</t>
   </si>
   <si>
     <t>QUALCOMM Incorporated</t>
   </si>
   <si>
-    <t>ASML Holding N.V. - New York Re</t>
+    <t>TSM</t>
   </si>
   <si>
     <t>AMD</t>
@@ -85,22 +88,22 @@
     <t>NVDA</t>
   </si>
   <si>
-    <t>TSM</t>
+    <t>ASML</t>
   </si>
   <si>
     <t>QCOM</t>
   </si>
   <si>
-    <t>ASML</t>
-  </si>
-  <si>
     <t>Pattern</t>
   </si>
   <si>
+    <t>📈 매수 관찰 구간입니다.</t>
+  </si>
+  <si>
     <t>⛔ 관망하십시오.</t>
   </si>
   <si>
-    <t>⚪ 중립 구간</t>
+    <t>🟢 상승 우위 (다소 완화)</t>
   </si>
 </sst>
 </file>
@@ -519,28 +522,28 @@
         <v>21</v>
       </c>
       <c r="D2">
-        <v>204.83</v>
+        <v>345.32</v>
       </c>
       <c r="E2">
-        <v>50.9</v>
+        <v>49.7</v>
       </c>
       <c r="F2">
-        <v>1.37</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="G2">
+        <v>60</v>
+      </c>
+      <c r="H2">
         <v>50</v>
       </c>
-      <c r="H2">
-        <v>83</v>
-      </c>
       <c r="I2">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="J2">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="K2">
-        <v>52.7</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="L2" t="s">
         <v>26</v>
@@ -549,10 +552,10 @@
         <v>27</v>
       </c>
       <c r="N2">
-        <v>41.81508460778518</v>
+        <v>66.57973643566133</v>
       </c>
       <c r="O2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -566,28 +569,28 @@
         <v>22</v>
       </c>
       <c r="D3">
-        <v>186.03</v>
+        <v>221.53</v>
       </c>
       <c r="E3">
-        <v>48.2</v>
+        <v>65.5</v>
       </c>
       <c r="F3">
-        <v>1.64</v>
+        <v>13</v>
       </c>
       <c r="G3">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="H3">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="I3">
         <v>56</v>
       </c>
       <c r="J3">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="K3">
-        <v>46.9</v>
+        <v>60.4</v>
       </c>
       <c r="L3" t="s">
         <v>26</v>
@@ -596,10 +599,10 @@
         <v>27</v>
       </c>
       <c r="N3">
-        <v>41.81508460778518</v>
+        <v>66.57973643566133</v>
       </c>
       <c r="O3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -613,40 +616,40 @@
         <v>23</v>
       </c>
       <c r="D4">
-        <v>354.56</v>
+        <v>178.1</v>
       </c>
       <c r="E4">
-        <v>47.2</v>
+        <v>45.5</v>
       </c>
       <c r="F4">
-        <v>-0.8100000000000001</v>
+        <v>7.83</v>
       </c>
       <c r="G4">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H4">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="I4">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="J4">
-        <v>76</v>
+        <v>43</v>
       </c>
       <c r="K4">
-        <v>43.7</v>
+        <v>59</v>
       </c>
       <c r="L4" t="s">
         <v>26</v>
       </c>
       <c r="M4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="N4">
-        <v>41.81508460778518</v>
+        <v>66.57973643566133</v>
       </c>
       <c r="O4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -660,40 +663,40 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>134.12</v>
+        <v>1306.45</v>
       </c>
       <c r="E5">
-        <v>38.8</v>
+        <v>41.5</v>
       </c>
       <c r="F5">
-        <v>-3.25</v>
+        <v>4.19</v>
       </c>
       <c r="G5">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H5">
+        <v>36</v>
+      </c>
+      <c r="I5">
         <v>50</v>
       </c>
-      <c r="I5">
-        <v>56</v>
-      </c>
       <c r="J5">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="K5">
-        <v>40.9</v>
+        <v>49</v>
       </c>
       <c r="L5" t="s">
         <v>26</v>
       </c>
       <c r="M5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="N5">
-        <v>41.81508460778518</v>
+        <v>66.57973643566133</v>
       </c>
       <c r="O5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:15">
@@ -707,40 +710,40 @@
         <v>25</v>
       </c>
       <c r="D6">
-        <v>1386.68</v>
+        <v>124.07</v>
       </c>
       <c r="E6">
-        <v>42.3</v>
+        <v>27.8</v>
       </c>
       <c r="F6">
-        <v>-0.91</v>
+        <v>-2.36</v>
       </c>
       <c r="G6">
         <v>20</v>
       </c>
       <c r="H6">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="I6">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="J6">
-        <v>83</v>
+        <v>43</v>
       </c>
       <c r="K6">
-        <v>40.9</v>
+        <v>44.4</v>
       </c>
       <c r="L6" t="s">
         <v>26</v>
       </c>
       <c r="M6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="N6">
-        <v>41.81508460778518</v>
+        <v>66.57973643566133</v>
       </c>
       <c r="O6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/DECISION/미장_반도체_분석.xlsx
+++ b/DECISION/미장_반도체_분석.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="29">
   <si>
     <t>날짜</t>
   </si>
@@ -61,49 +61,46 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-04-08</t>
+    <t>2026-05-07</t>
+  </si>
+  <si>
+    <t>Advanced Micro Devices, Inc.</t>
+  </si>
+  <si>
+    <t>ASML Holding N.V. - New York Re</t>
+  </si>
+  <si>
+    <t>QUALCOMM Incorporated</t>
+  </si>
+  <si>
+    <t>NVIDIA Corporation</t>
   </si>
   <si>
     <t>Taiwan Semiconductor Manufactur</t>
   </si>
   <si>
-    <t>Advanced Micro Devices, Inc.</t>
-  </si>
-  <si>
-    <t>NVIDIA Corporation</t>
-  </si>
-  <si>
-    <t>ASML Holding N.V. - New York Re</t>
-  </si>
-  <si>
-    <t>QUALCOMM Incorporated</t>
+    <t>AMD</t>
+  </si>
+  <si>
+    <t>ASML</t>
+  </si>
+  <si>
+    <t>QCOM</t>
+  </si>
+  <si>
+    <t>NVDA</t>
   </si>
   <si>
     <t>TSM</t>
   </si>
   <si>
-    <t>AMD</t>
-  </si>
-  <si>
-    <t>NVDA</t>
-  </si>
-  <si>
-    <t>ASML</t>
-  </si>
-  <si>
-    <t>QCOM</t>
-  </si>
-  <si>
     <t>Pattern</t>
   </si>
   <si>
-    <t>📈 매수 관찰 구간입니다.</t>
-  </si>
-  <si>
     <t>⛔ 관망하십시오.</t>
   </si>
   <si>
-    <t>🟢 상승 우위 (다소 완화)</t>
+    <t>⚪ 중립 구간</t>
   </si>
 </sst>
 </file>
@@ -522,28 +519,28 @@
         <v>21</v>
       </c>
       <c r="D2">
-        <v>345.32</v>
+        <v>421.39</v>
       </c>
       <c r="E2">
-        <v>49.7</v>
+        <v>80.2</v>
       </c>
       <c r="F2">
-        <v>9.109999999999999</v>
+        <v>25</v>
       </c>
       <c r="G2">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="H2">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="I2">
+        <v>73</v>
+      </c>
+      <c r="J2">
         <v>66</v>
       </c>
-      <c r="J2">
-        <v>70</v>
-      </c>
       <c r="K2">
-        <v>64.40000000000001</v>
+        <v>58.9</v>
       </c>
       <c r="L2" t="s">
         <v>26</v>
@@ -552,10 +549,10 @@
         <v>27</v>
       </c>
       <c r="N2">
-        <v>66.57973643566133</v>
+        <v>59.14876667115259</v>
       </c>
       <c r="O2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -569,28 +566,28 @@
         <v>22</v>
       </c>
       <c r="D3">
-        <v>221.53</v>
+        <v>1544.74</v>
       </c>
       <c r="E3">
-        <v>65.5</v>
+        <v>63.7</v>
       </c>
       <c r="F3">
-        <v>13</v>
+        <v>10.81</v>
       </c>
       <c r="G3">
+        <v>40</v>
+      </c>
+      <c r="H3">
         <v>60</v>
       </c>
-      <c r="H3">
-        <v>43</v>
-      </c>
       <c r="I3">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="J3">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="K3">
-        <v>60.4</v>
+        <v>56.1</v>
       </c>
       <c r="L3" t="s">
         <v>26</v>
@@ -599,10 +596,10 @@
         <v>27</v>
       </c>
       <c r="N3">
-        <v>66.57973643566133</v>
+        <v>59.14876667115259</v>
       </c>
       <c r="O3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -616,40 +613,40 @@
         <v>23</v>
       </c>
       <c r="D4">
-        <v>178.1</v>
+        <v>192.57</v>
       </c>
       <c r="E4">
-        <v>45.5</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="F4">
-        <v>7.83</v>
+        <v>23.44</v>
       </c>
       <c r="G4">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H4">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="I4">
         <v>60</v>
       </c>
       <c r="J4">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="K4">
-        <v>59</v>
+        <v>53.7</v>
       </c>
       <c r="L4" t="s">
         <v>26</v>
       </c>
       <c r="M4" t="s">
+        <v>27</v>
+      </c>
+      <c r="N4">
+        <v>59.14876667115259</v>
+      </c>
+      <c r="O4" t="s">
         <v>28</v>
-      </c>
-      <c r="N4">
-        <v>66.57973643566133</v>
-      </c>
-      <c r="O4" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -663,40 +660,40 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>1306.45</v>
+        <v>207.83</v>
       </c>
       <c r="E5">
-        <v>41.5</v>
+        <v>57.9</v>
       </c>
       <c r="F5">
-        <v>4.19</v>
+        <v>-0.68</v>
       </c>
       <c r="G5">
         <v>30</v>
       </c>
       <c r="H5">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="I5">
+        <v>60</v>
+      </c>
+      <c r="J5">
         <v>50</v>
       </c>
-      <c r="J5">
-        <v>70</v>
-      </c>
       <c r="K5">
-        <v>49</v>
+        <v>50.7</v>
       </c>
       <c r="L5" t="s">
         <v>26</v>
       </c>
       <c r="M5" t="s">
+        <v>27</v>
+      </c>
+      <c r="N5">
+        <v>59.14876667115259</v>
+      </c>
+      <c r="O5" t="s">
         <v>28</v>
-      </c>
-      <c r="N5">
-        <v>66.57973643566133</v>
-      </c>
-      <c r="O5" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:15">
@@ -710,40 +707,40 @@
         <v>25</v>
       </c>
       <c r="D6">
-        <v>124.07</v>
+        <v>419.5</v>
       </c>
       <c r="E6">
-        <v>27.8</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="F6">
-        <v>-2.36</v>
+        <v>6.52</v>
       </c>
       <c r="G6">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="H6">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="I6">
         <v>46</v>
       </c>
       <c r="J6">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="K6">
-        <v>44.4</v>
+        <v>48.1</v>
       </c>
       <c r="L6" t="s">
         <v>26</v>
       </c>
       <c r="M6" t="s">
+        <v>27</v>
+      </c>
+      <c r="N6">
+        <v>59.14876667115259</v>
+      </c>
+      <c r="O6" t="s">
         <v>28</v>
-      </c>
-      <c r="N6">
-        <v>66.57973643566133</v>
-      </c>
-      <c r="O6" t="s">
-        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/DECISION/미장_반도체_분석.xlsx
+++ b/DECISION/미장_반도체_분석.xlsx
@@ -61,46 +61,46 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-05-07</t>
+    <t>2026-06-07</t>
+  </si>
+  <si>
+    <t>Taiwan Semiconductor Manufactur</t>
+  </si>
+  <si>
+    <t>ASML Holding N.V. - New York Re</t>
   </si>
   <si>
     <t>Advanced Micro Devices, Inc.</t>
   </si>
   <si>
-    <t>ASML Holding N.V. - New York Re</t>
+    <t>NVIDIA Corporation</t>
   </si>
   <si>
     <t>QUALCOMM Incorporated</t>
   </si>
   <si>
-    <t>NVIDIA Corporation</t>
-  </si>
-  <si>
-    <t>Taiwan Semiconductor Manufactur</t>
+    <t>TSM</t>
+  </si>
+  <si>
+    <t>ASML</t>
   </si>
   <si>
     <t>AMD</t>
   </si>
   <si>
-    <t>ASML</t>
+    <t>NVDA</t>
   </si>
   <si>
     <t>QCOM</t>
   </si>
   <si>
-    <t>NVDA</t>
-  </si>
-  <si>
-    <t>TSM</t>
-  </si>
-  <si>
     <t>Pattern</t>
   </si>
   <si>
     <t>⛔ 관망하십시오.</t>
   </si>
   <si>
-    <t>⚪ 중립 구간</t>
+    <t>🔴 강한 긴축 / 리스크</t>
   </si>
 </sst>
 </file>
@@ -519,28 +519,28 @@
         <v>21</v>
       </c>
       <c r="D2">
-        <v>421.39</v>
+        <v>415.17</v>
       </c>
       <c r="E2">
-        <v>80.2</v>
+        <v>54.1</v>
       </c>
       <c r="F2">
-        <v>25</v>
+        <v>-0.78</v>
       </c>
       <c r="G2">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="H2">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="I2">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="J2">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="K2">
-        <v>58.9</v>
+        <v>46.9</v>
       </c>
       <c r="L2" t="s">
         <v>26</v>
@@ -549,7 +549,7 @@
         <v>27</v>
       </c>
       <c r="N2">
-        <v>59.14876667115259</v>
+        <v>13.11002090356014</v>
       </c>
       <c r="O2" t="s">
         <v>28</v>
@@ -566,28 +566,28 @@
         <v>22</v>
       </c>
       <c r="D3">
-        <v>1544.74</v>
+        <v>1641.74</v>
       </c>
       <c r="E3">
-        <v>63.7</v>
+        <v>63.3</v>
       </c>
       <c r="F3">
-        <v>10.81</v>
+        <v>1.8</v>
       </c>
       <c r="G3">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="H3">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="I3">
+        <v>53</v>
+      </c>
+      <c r="J3">
         <v>66</v>
       </c>
-      <c r="J3">
-        <v>70</v>
-      </c>
       <c r="K3">
-        <v>56.1</v>
+        <v>43.1</v>
       </c>
       <c r="L3" t="s">
         <v>26</v>
@@ -596,7 +596,7 @@
         <v>27</v>
       </c>
       <c r="N3">
-        <v>59.14876667115259</v>
+        <v>13.11002090356014</v>
       </c>
       <c r="O3" t="s">
         <v>28</v>
@@ -613,28 +613,28 @@
         <v>23</v>
       </c>
       <c r="D4">
-        <v>192.57</v>
+        <v>466.38</v>
       </c>
       <c r="E4">
-        <v>82.59999999999999</v>
+        <v>58.5</v>
       </c>
       <c r="F4">
-        <v>23.44</v>
+        <v>-9.630000000000001</v>
       </c>
       <c r="G4">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H4">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="I4">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="J4">
         <v>60</v>
       </c>
       <c r="K4">
-        <v>53.7</v>
+        <v>40.9</v>
       </c>
       <c r="L4" t="s">
         <v>26</v>
@@ -643,7 +643,7 @@
         <v>27</v>
       </c>
       <c r="N4">
-        <v>59.14876667115259</v>
+        <v>13.11002090356014</v>
       </c>
       <c r="O4" t="s">
         <v>28</v>
@@ -660,28 +660,28 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>207.83</v>
+        <v>205.1</v>
       </c>
       <c r="E5">
-        <v>57.9</v>
+        <v>34.3</v>
       </c>
       <c r="F5">
-        <v>-0.68</v>
+        <v>-2.75</v>
       </c>
       <c r="G5">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="I5">
+        <v>70</v>
+      </c>
+      <c r="J5">
         <v>60</v>
       </c>
-      <c r="J5">
-        <v>50</v>
-      </c>
       <c r="K5">
-        <v>50.7</v>
+        <v>31.9</v>
       </c>
       <c r="L5" t="s">
         <v>26</v>
@@ -690,7 +690,7 @@
         <v>27</v>
       </c>
       <c r="N5">
-        <v>59.14876667115259</v>
+        <v>13.11002090356014</v>
       </c>
       <c r="O5" t="s">
         <v>28</v>
@@ -707,28 +707,28 @@
         <v>25</v>
       </c>
       <c r="D6">
-        <v>419.5</v>
+        <v>215.94</v>
       </c>
       <c r="E6">
-        <v>74.59999999999999</v>
+        <v>54.4</v>
       </c>
       <c r="F6">
-        <v>6.52</v>
+        <v>-13.66</v>
       </c>
       <c r="G6">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H6">
         <v>50</v>
       </c>
       <c r="I6">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="J6">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="K6">
-        <v>48.1</v>
+        <v>28.9</v>
       </c>
       <c r="L6" t="s">
         <v>26</v>
@@ -737,7 +737,7 @@
         <v>27</v>
       </c>
       <c r="N6">
-        <v>59.14876667115259</v>
+        <v>13.11002090356014</v>
       </c>
       <c r="O6" t="s">
         <v>28</v>
